--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
@@ -41,6 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
@@ -55,12 +61,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC0CB"/>
         <bgColor rgb="00FFC0CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -155,28 +155,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -790,41 +790,73 @@
         </is>
       </c>
       <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E4" s="3" t="n">
+      <c r="D4" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" s="13" t="n">
         <v>13.6</v>
       </c>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
+      <c r="F4" s="13" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="H4" s="3" t="n">
         <v>13.1</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
+      <c r="J4" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n">
         <v>14.5</v>
       </c>
-      <c r="O4" s="3" t="n"/>
-      <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="n"/>
+      <c r="O4" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="R4" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" s="3" t="n"/>
-      <c r="U4" s="3" t="n"/>
-      <c r="V4" s="3" t="n"/>
-      <c r="W4" s="3" t="n"/>
-      <c r="X4" s="3" t="n"/>
-      <c r="Y4" s="3" t="n"/>
-      <c r="Z4" s="3" t="n"/>
+      <c r="S4" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -838,59 +870,75 @@
           <t>2</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>44.1</v>
+      <c r="C5" s="3" t="n">
+        <v>508.2</v>
+      </c>
+      <c r="D5" s="13" t="n"/>
+      <c r="E5" s="3" t="n">
+        <v>14.2</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="8" t="n">
-        <v>12.8</v>
+      <c r="G5" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
+        <v>2.5</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>14.6</v>
+      </c>
       <c r="N5" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n"/>
+        <v>6.1</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>22.4</v>
+      </c>
       <c r="R5" s="3" t="n">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>16.5</v>
+        <v>17.6</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>52</v>
+        <v>61.5</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>8.9</v>
+        <v>10.4</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>17.6</v>
+        <v>16.8</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="Y5" s="3" t="n"/>
+        <v>18.3</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>27</v>
+      </c>
       <c r="Z5" s="3" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -906,56 +954,74 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1208.9</v>
-      </c>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="11" t="n">
-        <v>44.1</v>
+        <v>52.9</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>24.41</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G6" s="3" t="n"/>
-      <c r="H6" s="8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>41.8</v>
+      </c>
       <c r="M6" s="8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N6" s="3" t="n"/>
+        <v>31.8</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>92</v>
+      </c>
       <c r="O6" s="3" t="n"/>
-      <c r="P6" s="3" t="n"/>
-      <c r="Q6" s="3" t="n"/>
+      <c r="P6" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="Q6" s="8" t="n">
+        <v>43.6</v>
+      </c>
       <c r="R6" s="3" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>99.7</v>
+        <v>13.5</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>6150.1</v>
+        <v>59.1</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="V6" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>18.7</v>
+      </c>
       <c r="W6" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X6" s="8" t="n">
-        <v>432.1</v>
-      </c>
-      <c r="Y6" s="3" t="n"/>
+        <v>16.6</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>82.5</v>
+      </c>
       <c r="Z6" s="3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -971,48 +1037,76 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>171.5</v>
-      </c>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
+        <v>22.8</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="F7" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="G7" s="3" t="n"/>
-      <c r="H7" s="3" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="I7" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="J7" s="3" t="n"/>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
+        <v>2.8</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>718.1</v>
+      </c>
       <c r="P7" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>77.59999999999999</v>
+      </c>
       <c r="S7" s="3" t="n">
-        <v>9.9</v>
+        <v>17.4</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>64</v>
       </c>
-      <c r="U7" s="3" t="n"/>
+      <c r="U7" s="3" t="n">
+        <v>97.8</v>
+      </c>
       <c r="V7" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="W7" s="8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="X7" s="8" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="Y7" s="3" t="n"/>
+        <v>19.2</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>20.8</v>
+      </c>
       <c r="Z7" s="3" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1028,53 +1122,75 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
+        <v>24.9</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="F8" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>12.7</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H8" s="3" t="n"/>
+        <v>7.2</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="I8" s="3" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>164.1</v>
-      </c>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>15.1</v>
+      </c>
       <c r="M8" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N8" s="3" t="n"/>
+        <v>14.6</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="O8" s="3" t="n"/>
-      <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="3" t="n"/>
+      <c r="P8" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>20.5</v>
+      </c>
       <c r="R8" s="3" t="n">
-        <v>882.1</v>
+        <v>17.5</v>
       </c>
       <c r="S8" s="3" t="n">
-        <v>36.9</v>
+        <v>18.5</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="U8" s="3" t="n"/>
+        <v>76</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>5.8</v>
+      </c>
       <c r="V8" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="W8" s="8" t="n">
-        <v>16.8</v>
+        <v>17.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>16</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1091,54 +1207,76 @@
       <c r="C9" s="3" t="n">
         <v>445</v>
       </c>
-      <c r="D9" s="10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="F9" s="12" t="n"/>
+      <c r="D9" s="13" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>67.59999999999999</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>9.199999999999999</v>
+      </c>
       <c r="G9" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
+        <v>9.1</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>63.1</v>
+      </c>
       <c r="I9" s="3" t="n">
+        <v>206.1</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17179190
+1
+</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="n"/>
+      <c r="M9" s="3" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="N9" s="3" t="n">
         <v>1.1</v>
       </c>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
+      <c r="O9" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="P9" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="Q9" s="3" t="n"/>
+        <v>0.7</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>173.8</v>
+      </c>
       <c r="R9" s="3" t="n">
-        <v>17.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>17.2</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="U9" s="3" t="n"/>
+        <v>7.6</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="V9" s="3" t="n">
-        <v>194</v>
+        <v>40.1</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>88.8</v>
+        <v>82.8</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>89.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>23</v>
+        <v>45.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>3.8</v>
+        <v>19.4</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1154,55 +1292,77 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="3" t="n">
-        <v>18.1</v>
+        <v>194.8</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>1.6</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H10" s="3" t="n"/>
-      <c r="I10" s="3" t="n"/>
+        <v>1.2</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="J10" s="3" t="n">
-        <v>164.1</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="M10" s="3" t="n"/>
+        <v>3.3</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>13.8</v>
+      </c>
       <c r="N10" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="8" t="n">
-        <v>119.3</v>
+        <v>0.8</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>880.1</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="S10" s="8" t="n">
-        <v>19</v>
+        <v>7.6</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>7.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U10" s="3" t="n"/>
-      <c r="V10" s="8" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V10" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="W10" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="Y10" s="3" t="n"/>
-      <c r="Z10" s="3" t="n"/>
+        <v>1.9</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1216,59 +1376,81 @@
           <t>6</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H11" s="3" t="n"/>
-      <c r="I11" s="3" t="n"/>
+      <c r="C11" s="3" t="n">
+        <v>298.9</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="J11" s="3" t="n">
-        <v>1.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>14.3</v>
+        <v>28.2</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="3" t="n"/>
+        <v>468.6</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>19.3</v>
+      </c>
       <c r="R11" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>17.7</v>
+        <v>12.5</v>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+198
+</t>
+        </is>
       </c>
       <c r="T11" s="3" t="n">
-        <v>42.6</v>
-      </c>
-      <c r="U11" s="3" t="n"/>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>3.4</v>
+      </c>
       <c r="V11" s="3" t="n">
-        <v>41.6</v>
+        <v>1.5</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>88.8</v>
+        <v>13.7</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>4.1</v>
+        <v>1.8</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1284,60 +1466,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="D12" s="9" t="n"/>
+        <v>298.9</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>2.9</v>
+      </c>
       <c r="E12" s="3" t="n">
-        <v>15.7</v>
+        <v>18.5</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>17.6</v>
+        <v>17.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>11.2</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K12" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="L12" s="3" t="n">
-        <v>241.4</v>
-      </c>
-      <c r="M12" s="3" t="n"/>
-      <c r="N12" s="3" t="n"/>
+        <v>14.8</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>10.2</v>
+      </c>
       <c r="O12" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="8" t="n">
-        <v>121.3</v>
+        <v>94.5</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>20.3</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>17.6</v>
+        <v>14.1</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>16.3</v>
+        <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>920.5</v>
-      </c>
-      <c r="U12" s="3" t="n"/>
-      <c r="V12" s="8" t="n">
-        <v>18.8</v>
+        <v>4.5</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="V12" s="3" t="n">
+        <v>16.5</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>15.1</v>
+        <v>14.8</v>
       </c>
       <c r="X12" s="3" t="n">
-        <v>15.9</v>
+        <v>1.5</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1352,63 +1550,73 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="3" t="n">
-        <v>14.1</v>
+      <c r="C13" s="3" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>18.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L13" s="8" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M13" s="8" t="n">
-        <v>13.8</v>
+        <v>49.8</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>14.4</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>16.8</v>
+        <v>1.1</v>
       </c>
       <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
+      <c r="P13" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q13" s="8" t="n">
-        <v>119.3</v>
+        <v>58.2</v>
       </c>
       <c r="R13" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="Z13" s="3" t="n">
         <v>1.6</v>
-      </c>
-      <c r="S13" s="8" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="T13" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="W13" s="8" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="Y13" s="3" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="Z13" s="3" t="n">
-        <v>12.8</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1424,64 +1632,74 @@
         </is>
       </c>
       <c r="C14" s="3" t="n"/>
-      <c r="D14" s="11" t="n">
-        <v>17.46</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>91.8</v>
+      <c r="D14" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>44.5</v>
+        <v>8.9</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>5.3</v>
+      </c>
       <c r="L14" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M14" s="8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
+        <v>14.4</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>6.6</v>
+      </c>
       <c r="P14" s="3" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>96.5</v>
+        <v>41.3</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>83.5</v>
+        <v>17.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>16.9</v>
+        <v>18.1</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>2.5</v>
+        <v>28.8</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>44.8</v>
+        <v>2.1</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>41.6</v>
+        <v>18.2</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>23.1</v>
+        <v>16.6</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>92</v>
+        <v>8.5</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>11.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1497,71 +1715,72 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>22.5</v>
+        <v>1475.5</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255 8
-</t>
-        </is>
+        <v>24.8</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>1.3</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="I15" s="3" t="n"/>
+        <v>12.6</v>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>12.1</v>
+      </c>
       <c r="J15" s="3" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5.4</v>
+        <v>0.4</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>241.4</v>
+        <v>14.6</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="Q15" s="3" t="n">
         <v>19.8</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>88</v>
+        <v>16.9</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>373</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V15" s="3" t="n"/>
+        <v>6.2</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>16.6</v>
+      </c>
       <c r="W15" s="3" t="n">
         <v>15.7</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>20.1</v>
+        <v>1.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>45.8</v>
+        <v>341</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1577,72 +1796,78 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>17.6</v>
+        <v>141.6</v>
+      </c>
+      <c r="D16" s="15" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>91.09999999999999</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>19.5</v>
+        <v>47.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>10.9</v>
+        <v>644.1</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>2.2</v>
+        <v>5.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>6.9</v>
+      </c>
+      <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n">
-        <v>14</v>
+        <v>73.2</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>113</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
+        <v>69.40000000000001</v>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5117
+18
+</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="P16" s="3" t="n"/>
+        <v>2.9</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="Q16" s="3" t="n">
-        <v>121.8</v>
+        <v>0.7</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>17.8</v>
+        <v>23.4</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>17.6</v>
+        <v>88</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>5.4</v>
+        <v>3994.5</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>18.1</v>
+        <v>84.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>116</v>
+        <v>25.6</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>17.2</v>
+        <v>56.1</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>9.1</v>
+        <v>48.2</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1657,61 +1882,75 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="10" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="10" t="n">
-        <v>19.5</v>
+      <c r="C17" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>24</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>48.1</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="I17" s="3" t="n"/>
-      <c r="J17" s="3" t="n"/>
+        <v>29.5</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="K17" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L17" s="8" t="n">
-        <v>15.1</v>
+        <v>0.4</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
-      <c r="P17" s="3" t="n"/>
-      <c r="Q17" s="3" t="n"/>
+      <c r="O17" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>19.3</v>
+      </c>
       <c r="R17" s="3" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
-        <v>78.09999999999999</v>
+        <v>17.6</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>16.2</v>
+        <v>8.9</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="W17" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="X17" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="X17" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="Y17" s="3" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>40.1</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1726,63 +1965,75 @@
           <t>11</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="11" t="n">
-        <v>17.46</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="G18" s="8" t="n">
-        <v>17</v>
+      <c r="C18" s="3" t="n">
+        <v>428.5</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>6.8</v>
+        <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J18" s="3" t="n"/>
-      <c r="K18" s="3" t="n"/>
+        <v>8.1</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>18.7</v>
+      </c>
       <c r="L18" s="3" t="n">
-        <v>15.4</v>
+        <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="N18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
-      <c r="P18" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P18" s="3" t="n"/>
+      <c r="Q18" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W18" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="Q18" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="R18" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S18" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="T18" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="V18" s="3" t="n"/>
-      <c r="W18" s="3" t="n">
-        <v>16.8</v>
-      </c>
       <c r="X18" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="Y18" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>81</v>
+      </c>
       <c r="Z18" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>410.4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1798,55 +2049,78 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255 8
+        <v>440.6</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+7
 </t>
         </is>
       </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="M19" s="3" t="n"/>
-      <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="n"/>
-      <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="3" t="n"/>
+      <c r="P19" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>24.9</v>
+      </c>
       <c r="R19" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="T19" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="U19" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v>18.5</v>
+        <v>1.4</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>17</v>
+        <v>12.2</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>5.5</v>
+        <v>810.5</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -1862,72 +2136,74 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>0.1</v>
+        <v>15.1</v>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>1.5</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>43.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="8" t="n">
-        <v>10.5</v>
+        <v>23.8</v>
+      </c>
+      <c r="I20" s="3" t="n"/>
+      <c r="J20" s="3" t="n"/>
+      <c r="K20" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>15.4</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="N20" s="3" t="n">
-        <v>1.6</v>
+        <v>15.1</v>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+7
+</t>
+        </is>
       </c>
       <c r="O20" s="3" t="n"/>
       <c r="P20" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q20" s="8" t="n">
-        <v>120.4</v>
+        <v>1.5</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>20.5</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>17.6</v>
+        <v>18.5</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>46.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>5</v>
+        <v>18.5</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>17.5</v>
+        <v>12.6</v>
       </c>
       <c r="W20" s="3" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>10.2</v>
+        <v>18.6</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>9.1</v>
+        <v>92</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>40.1</v>
+        <v>11.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -1942,65 +2218,77 @@
           <t>14</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="G21" s="3" t="n"/>
+      <c r="C21" s="3" t="n">
+        <v>2461.7</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>7.2</v>
+      </c>
       <c r="H21" s="3" t="n">
-        <v>10.9</v>
+        <v>14.1</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J21" s="3" t="n"/>
+        <v>1.1</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>11.5</v>
+      </c>
       <c r="K21" s="3" t="n">
-        <v>284.4</v>
+        <v>3</v>
       </c>
       <c r="L21" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="X21" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="M21" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="N21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
-      <c r="P21" s="3" t="n"/>
-      <c r="Q21" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="S21" s="3" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="T21" s="3" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="U21" s="3" t="n">
-        <v>40.6</v>
-      </c>
-      <c r="V21" s="3" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="W21" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>17</v>
-      </c>
       <c r="Y21" s="3" t="n">
-        <v>438.5</v>
+        <v>4.8</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2016,60 +2304,70 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>17</v>
+        <v>13.3</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>6.2</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="I22" s="3" t="n"/>
-      <c r="J22" s="3" t="n"/>
-      <c r="K22" s="3" t="n"/>
+        <v>13.4</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>33.2</v>
+      </c>
       <c r="L22" s="3" t="n">
-        <v>15.2</v>
+        <v>1.5</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="N22" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>14.6</v>
+      </c>
+      <c r="N22" s="3" t="n"/>
       <c r="O22" s="3" t="n"/>
-      <c r="P22" s="3" t="n"/>
-      <c r="Q22" s="3" t="n"/>
+      <c r="P22" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>26.4</v>
+      </c>
       <c r="R22" s="3" t="n">
-        <v>17.8</v>
+        <v>17.2</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>18.1</v>
+        <v>1.8</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="U22" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>56.2</v>
+      </c>
       <c r="V22" s="3" t="n">
-        <v>18.3</v>
+        <v>1.5</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X22" s="3" t="n">
-        <v>18.7</v>
-      </c>
+        <v>16.9</v>
+      </c>
+      <c r="X22" s="3" t="n"/>
       <c r="Y22" s="3" t="n">
-        <v>0.8</v>
+        <v>45.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>2.8</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2085,62 +2383,68 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1326.8</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="G23" s="16" t="n">
-        <v>9.6</v>
+        <v>147.7</v>
+      </c>
+      <c r="D23" s="15" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n"/>
-      <c r="I23" s="3" t="n">
-        <v>0.8</v>
-      </c>
+      <c r="I23" s="3" t="n"/>
       <c r="J23" s="3" t="n">
-        <v>2</v>
+        <v>7.3</v>
       </c>
       <c r="K23" s="3" t="n"/>
       <c r="L23" s="3" t="n">
-        <v>115.1</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>114.2</v>
-      </c>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
-      <c r="P23" s="3" t="n"/>
+        <v>76.2</v>
+      </c>
+      <c r="M23" s="3" t="n"/>
+      <c r="N23" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="Q23" s="3" t="n">
-        <v>0.8</v>
+        <v>179.8</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>17.6</v>
+        <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>17.8</v>
+        <v>90.2</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="U23" s="3" t="n"/>
+        <v>41.9</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>40.6</v>
+      </c>
       <c r="V23" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>44.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>15.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="Y23" s="3" t="n"/>
+        <v>2.3</v>
+      </c>
+      <c r="Y23" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Z23" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>158.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2156,60 +2460,72 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="10" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F24" s="11" t="n">
-        <v>1</v>
+        <v>1.4</v>
+      </c>
+      <c r="D24" s="15" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E24" s="14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <v>18.3</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="I24" s="3" t="n"/>
-      <c r="J24" s="3" t="n"/>
+        <v>0.8</v>
+      </c>
+      <c r="H24" s="3" t="n"/>
+      <c r="I24" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>1.9</v>
+      </c>
       <c r="K24" s="3" t="n"/>
-      <c r="L24" s="8" t="n">
-        <v>184.6</v>
-      </c>
-      <c r="M24" s="3" t="n"/>
+      <c r="L24" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+111
+</t>
+        </is>
+      </c>
       <c r="P24" s="3" t="n"/>
       <c r="Q24" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R24" s="8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="S24" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>17.8</v>
       </c>
+      <c r="S24" s="8" t="n">
+        <v>28.1</v>
+      </c>
       <c r="T24" s="3" t="n">
-        <v>7301</v>
+        <v>9.6</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v>17.9</v>
+        <v>8.1</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>16.5</v>
+        <v>1.8</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>18</v>
+        <v>11.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>1.8</v>
+        <v>94</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>12.6</v>
+        <v>2.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2225,70 +2541,70 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>17.9</v>
+        <v>4.6</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E25" s="14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>1.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1.5</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>11.6</v>
+        <v>0.8</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="L25" s="8" t="n">
-        <v>10.5</v>
+        <v>1</v>
+      </c>
+      <c r="K25" s="3" t="n"/>
+      <c r="L25" s="3" t="n">
+        <v>45.1</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="N25" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>145.4</v>
+      </c>
+      <c r="R25" s="3" t="n"/>
+      <c r="S25" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="Z25" s="3" t="n">
         <v>1.6</v>
-      </c>
-      <c r="O25" s="3" t="n"/>
-      <c r="P25" s="3" t="n"/>
-      <c r="Q25" s="8" t="n">
-        <v>120.7</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="T25" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="U25" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>94.40000000000001</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Y25" s="3" t="n"/>
-      <c r="Z25" s="3" t="n">
-        <v>40.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2303,67 +2619,81 @@
           <t>17</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="9" t="n"/>
+      <c r="C26" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <v>2.5</v>
+      </c>
       <c r="E26" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F26" s="11" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n">
-        <v>284.4</v>
+        <v>1.4</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+1198
+</t>
+        </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>16.4</v>
+        <v>14.1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O26" s="3" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>40.6</v>
+      </c>
       <c r="P26" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q26" s="8" t="n">
-        <v>210.8</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="S26" s="8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="S26" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v>12.9</v>
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>6.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>18.8</v>
+        <v>12.5</v>
       </c>
       <c r="W26" s="3" t="n">
-        <v>17.1</v>
+        <v>46.5</v>
       </c>
       <c r="X26" s="3" t="n">
         <v>18.5</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>438.5</v>
+        <v>91.8</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>7.5</v>
+        <v>2.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2379,60 +2709,74 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>95.40000000000001</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E27" s="3" t="n"/>
-      <c r="F27" s="8" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="G27" s="8" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="H27" s="8" t="n">
-        <v>86.59999999999999</v>
+        <v>53.5</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>14.9</v>
       </c>
       <c r="I27" s="3" t="n"/>
       <c r="J27" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="M27" s="3" t="n"/>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
+        <v>2.1</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>95</v>
+      </c>
       <c r="P27" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q27" s="3" t="n"/>
+        <v>16.8</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>20.8</v>
+      </c>
       <c r="R27" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V27" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="S27" s="8" t="n">
-        <v>82.09999999999999</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="U27" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="V27" s="3" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="W27" s="3" t="n"/>
+      <c r="W27" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="X27" s="3" t="n">
-        <v>88.7</v>
+        <v>15.8</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>142.8</v>
+        <v>83.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>73.8</v>
+        <v>2</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2448,59 +2792,81 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>1326.8</v>
-      </c>
-      <c r="D28" s="16" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F28" s="16" t="n">
-        <v>18.1</v>
+        <v>289.8</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>1.9</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
+        <v>28</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>8.6</v>
+      </c>
       <c r="J28" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" s="3" t="n"/>
-      <c r="L28" s="8" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M28" s="8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9799791979277
+2 8
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M28" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="N28" s="3" t="n"/>
-      <c r="O28" s="3" t="n"/>
-      <c r="P28" s="3" t="n"/>
-      <c r="Q28" s="8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="R28" s="3" t="n"/>
+      <c r="N28" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="P28" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>17</v>
+      </c>
       <c r="S28" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v>34.6</v>
+        <v>2.8</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>6.6</v>
       </c>
       <c r="V28" s="3" t="n">
-        <v>11.6</v>
+        <v>16.7</v>
       </c>
       <c r="W28" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X28" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="Y28" s="3" t="n"/>
-      <c r="Z28" s="3" t="n"/>
+        <v>14.8</v>
+      </c>
+      <c r="X28" s="8" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2514,61 +2880,73 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="8" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F29" s="9" t="n"/>
-      <c r="G29" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
+      <c r="C29" s="3" t="n">
+        <v>199.9</v>
+      </c>
+      <c r="D29" s="13" t="n">
+        <v>22</v>
+      </c>
+      <c r="E29" s="13" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G29" s="13" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="J29" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K29" s="3" t="n"/>
+        <v>2.6</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>25</v>
+      </c>
       <c r="L29" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="M29" s="3" t="n"/>
-      <c r="N29" s="3" t="n"/>
+        <v>14.9</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>714.4</v>
+      </c>
       <c r="O29" s="3" t="n">
-        <v>941.4</v>
-      </c>
-      <c r="P29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="R29" s="8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="S29" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P29" s="3" t="n"/>
+      <c r="Q29" s="3" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="R29" s="3" t="n">
         <v>17.8</v>
       </c>
+      <c r="S29" s="8" t="n">
+        <v>12.1</v>
+      </c>
       <c r="T29" s="3" t="n">
-        <v>7301</v>
+        <v>1.8</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>64.7</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>17.9</v>
+        <v>0.8</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="W29" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="X29" s="8" t="n">
-        <v>18</v>
-      </c>
+        <v>17.1</v>
+      </c>
+      <c r="X29" s="3" t="n"/>
       <c r="Y29" s="3" t="n">
-        <v>1.8</v>
+        <v>147.4</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>12.6</v>
+        <v>3.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2583,60 +2961,91 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="10" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>1.5</v>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1921
+188181
+</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>68.59999999999999</v>
+      </c>
+      <c r="F30" s="15" t="n">
+        <v>966.1</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <v>457</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="I30" s="3" t="n"/>
-      <c r="J30" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="L30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="N30" s="3" t="n"/>
-      <c r="O30" s="3" t="n"/>
-      <c r="P30" s="3" t="n"/>
+        <v>6661.1</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="J30" s="3" t="n"/>
+      <c r="K30" s="3" t="n"/>
+      <c r="L30" s="3" t="n">
+        <v>719.7</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Q30" s="3" t="n">
-        <v>1120.7</v>
+        <v>15.2</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="T30" s="3" t="n">
-        <v>79</v>
+        <v>824.4</v>
+      </c>
+      <c r="S30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">368883
+101
+</t>
+        </is>
+      </c>
+      <c r="T30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9242175
+993 6
+</t>
+        </is>
       </c>
       <c r="U30" s="3" t="n">
-        <v>1.5</v>
+        <v>246.1</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>94.40000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v>42.2</v>
-      </c>
-      <c r="Y30" s="3" t="n"/>
-      <c r="Z30" s="3" t="n"/>
+        <v>84.09999999999999</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+1
+17
+</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>75.09999999999999</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2650,58 +3059,74 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="11" t="n">
+      <c r="C31" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="D31" s="13" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F31" s="15" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G31" s="13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O31" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="E31" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="3" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="M31" s="3" t="n"/>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
       <c r="P31" s="3" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>17</v>
+        <v>2.1</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>15.8</v>
+        <v>17.5</v>
       </c>
       <c r="S31" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="T31" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="U31" s="8" t="n">
-        <v>12.9</v>
+      <c r="T31" s="3" t="n"/>
+      <c r="U31" s="3" t="n">
+        <v>6.9</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>15.9</v>
+        <v>1.6</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y31" s="3" t="n"/>
-      <c r="Z31" s="3" t="n"/>
+        <v>6.2</v>
+      </c>
+      <c r="X31" s="3" t="n"/>
+      <c r="Y31" s="3" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2715,51 +3140,81 @@
           <t>21</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
+      <c r="C32" s="3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="D32" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="F32" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G32" s="8" t="n">
-        <v>43.7</v>
-      </c>
-      <c r="H32" s="3" t="n"/>
+        <v>13.1</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>15.4</v>
+      </c>
       <c r="I32" s="3" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="K32" s="3" t="n"/>
+        <v>6.8</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.7</v>
+      </c>
       <c r="L32" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M32" s="3" t="n"/>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
-      <c r="P32" s="3" t="n"/>
-      <c r="Q32" s="3" t="n"/>
+        <v>1.3</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>445.1</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>17</v>
+      </c>
       <c r="R32" s="3" t="n">
-        <v>17.8</v>
+        <v>15.8</v>
       </c>
       <c r="S32" s="8" t="n">
-        <v>82.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="3" t="n"/>
-      <c r="X32" s="8" t="n">
-        <v>246.4</v>
-      </c>
-      <c r="Y32" s="3" t="n"/>
+        <v>51.5</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+710
+</t>
+        </is>
+      </c>
       <c r="Z32" s="3" t="n">
-        <v>73.8</v>
+        <v>8.5</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -2774,56 +3229,78 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="8" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="3" t="n"/>
+      <c r="C33" s="3" t="n">
+        <v>482.8</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="H33" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="I33" s="3" t="n"/>
+        <v>22.5</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>22.6</v>
+      </c>
       <c r="J33" s="3" t="n">
-        <v>0.5</v>
+        <v>14.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
+        <v>20</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="P33" s="3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q33" s="8" t="n">
-        <v>15.2</v>
+        <v>1</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>6.9</v>
+        <v>16.8</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>91.8</v>
+        <v>1.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>111.2</v>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v>34.6</v>
+        <v>51.5</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>1.8</v>
       </c>
       <c r="V33" s="3" t="n">
-        <v>87.8</v>
-      </c>
-      <c r="W33" s="3" t="n"/>
+        <v>11.6</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>15.4</v>
+      </c>
       <c r="X33" s="3" t="n">
-        <v>88.7</v>
+        <v>16.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>142.8</v>
-      </c>
-      <c r="Z33" s="3" t="n"/>
+        <v>80.8</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
           <t>22</t>
@@ -2838,63 +3315,88 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="D34" s="11" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="E34" s="11" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="F34" s="11" t="n">
-        <v>81.5</v>
+        <v>482.8</v>
+      </c>
+      <c r="D34" s="13" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E34" s="13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>17.8</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H34" s="3" t="n"/>
-      <c r="I34" s="3" t="n"/>
+        <v>1.6</v>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112179 1
+</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>2.5</v>
+      </c>
       <c r="J34" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K34" s="3" t="n"/>
+        <v>3.9</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>20</v>
+      </c>
       <c r="L34" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="M34" s="3" t="n"/>
-      <c r="N34" s="3" t="n"/>
+        <v>12.5</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+1
+</t>
+        </is>
+      </c>
       <c r="O34" s="3" t="n">
-        <v>941.4</v>
+        <v>92</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="R34" s="8" t="n">
-        <v>18.8</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>18.5</v>
+        <v>15.2</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>1.2</v>
+        <v>714.4</v>
       </c>
       <c r="U34" s="3" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>11.6</v>
+        <v>18</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y34" s="3" t="n"/>
-      <c r="Z34" s="3" t="n"/>
+        <v>16.7</v>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+247
+</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>4.2</v>
+      </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
           <t>23</t>
@@ -2909,57 +3411,81 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>44224.1</v>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F35" s="16" t="n">
-        <v>19.1</v>
+        <v>492.8</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <v>93.7</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H35" s="3" t="n"/>
+        <v>11.4</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>12.5</v>
+      </c>
       <c r="I35" s="3" t="n">
-        <v>0.2</v>
+        <v>2.4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>38.1</v>
-      </c>
-      <c r="K35" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>20</v>
+      </c>
       <c r="L35" s="3" t="n">
         <v>16.6</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="N35" s="3" t="n"/>
-      <c r="O35" s="3" t="n"/>
-      <c r="P35" s="3" t="n"/>
-      <c r="Q35" s="3" t="n">
-        <v>17</v>
+        <v>15.5</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14181
+60
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>45.7</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>15.8</v>
+        <v>18.8</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>11</v>
+        <v>16.8</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U35" s="3" t="n"/>
-      <c r="V35" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="W35" s="3" t="n"/>
-      <c r="X35" s="3" t="n"/>
-      <c r="Y35" s="3" t="n"/>
-      <c r="Z35" s="3" t="n"/>
+        <v>56.8</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>85.09999999999999</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>6</v>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -2973,62 +3499,75 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n"/>
-      <c r="D36" s="8" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="G36" s="3" t="n"/>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 7
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>2.6</v>
+      <c r="C36" s="3" t="n">
+        <v>498.9</v>
+      </c>
+      <c r="D36" s="13" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E36" s="13" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G36" s="13" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>23.5</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>4</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="M36" s="3" t="n"/>
+        <v>16.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>15.6</v>
+      </c>
       <c r="N36" s="3" t="n"/>
-      <c r="O36" s="3" t="n"/>
+      <c r="O36" s="3" t="n">
+        <v>918</v>
+      </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" s="3" t="n">
-        <v>13.4</v>
+        <v>1.6</v>
+      </c>
+      <c r="Q36" s="8" t="n">
+        <v>44.1</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>37.7</v>
-      </c>
-      <c r="S36" s="3" t="n">
-        <v>91.8</v>
+        <v>17.9</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>82.8</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V36" s="3" t="n"/>
-      <c r="W36" s="3" t="n"/>
-      <c r="X36" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="Y36" s="3" t="n"/>
+        <v>60.8</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X36" s="8" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>79.8</v>
+      </c>
       <c r="Z36" s="3" t="n">
-        <v>18.1</v>
+        <v>4.8</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3044,63 +3583,73 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>11108</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>43.6</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>0.1</v>
+        <v>928</v>
+      </c>
+      <c r="D37" s="15" t="n">
+        <v>119.4</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H37" s="3" t="n"/>
+        <v>53.3</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>613.9</v>
+      </c>
       <c r="I37" s="3" t="n">
-        <v>10.6</v>
+        <v>1.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>224.1</v>
-      </c>
-      <c r="K37" s="3" t="n"/>
+        <v>0.6</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>12.1</v>
+      </c>
       <c r="L37" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>10</v>
-      </c>
+        <v>75.7</v>
+      </c>
+      <c r="M37" s="3" t="n"/>
       <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="P37" s="3" t="n"/>
-      <c r="Q37" s="3" t="n"/>
+        <v>4498</v>
+      </c>
+      <c r="P37" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>11.3</v>
+      </c>
       <c r="R37" s="3" t="n">
-        <v>118.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>111.2</v>
+        <v>58.1</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="V37" s="3" t="n"/>
+        <v>4.8</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>377.1</v>
+      </c>
       <c r="W37" s="3" t="n">
-        <v>26.2</v>
+        <v>804.8</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>12.1</v>
+        <v>85.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z37" s="3" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -3114,50 +3663,87 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n"/>
-      <c r="D38" s="10" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="E38" s="10" t="n">
+      <c r="C38" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D38" s="15" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E38" s="15" t="n">
         <v>13.2</v>
       </c>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="3" t="n"/>
+      <c r="F38" s="15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G38" s="13" t="n">
+        <v>10.6</v>
+      </c>
       <c r="H38" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>6.4</v>
+        <v>2.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>35</v>
+        <v>3.5</v>
       </c>
       <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="n"/>
-      <c r="M38" s="3" t="n"/>
-      <c r="N38" s="3" t="n"/>
-      <c r="O38" s="3" t="n"/>
-      <c r="P38" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="3" t="n"/>
-      <c r="R38" s="3" t="n"/>
+      <c r="L38" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M38" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61718682
+68
+8987
+</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4 8
+21 0
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+14
+</t>
+        </is>
+      </c>
       <c r="S38" s="3" t="n">
-        <v>11</v>
+        <v>84.8</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>111.8</v>
+        <v>31.4</v>
       </c>
       <c r="U38" s="3" t="n"/>
       <c r="V38" s="3" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="W38" s="3" t="n"/>
-      <c r="X38" s="3" t="n">
-        <v>46</v>
-      </c>
-      <c r="Y38" s="3" t="n"/>
-      <c r="Z38" s="3" t="n"/>
+        <v>18.2</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="X38" s="8" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>81.90000000000001</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3172,60 +3758,78 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="3" t="n">
-        <v>13</v>
+        <v>58.3</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>1</v>
       </c>
       <c r="F39" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="G39" s="3" t="n"/>
-      <c r="H39" s="3" t="n"/>
+      <c r="G39" s="3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="I39" s="3" t="n">
-        <v>10.6</v>
+        <v>71.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>224.1</v>
-      </c>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
+        <v>5.7</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="M39" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="N39" s="3" t="n"/>
-      <c r="O39" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="P39" s="3" t="n"/>
-      <c r="Q39" s="3" t="n">
-        <v>13.4</v>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+8917
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>53.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>16.6</v>
+        <v>11.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>52</v>
+        <v>64.7</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>19.2</v>
+        <v>11.4</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>1.2</v>
+        <v>16</v>
       </c>
       <c r="X39" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>0.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>18.1</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3240,48 +3844,82 @@
           <t>27</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n"/>
-      <c r="D40" s="8" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E40" s="3" t="n">
+      <c r="C40" s="3" t="n">
+        <v>545.1</v>
+      </c>
+      <c r="D40" s="13" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="E40" s="13" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G40" s="13" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="I40" s="8" t="n">
+        <v>353</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="8" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>353.6</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+6
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q40" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="F40" s="9" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L40" s="3" t="n"/>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
-      <c r="O40" s="3" t="n"/>
-      <c r="P40" s="3" t="n"/>
-      <c r="Q40" s="3" t="n"/>
-      <c r="R40" s="3" t="n"/>
+      <c r="R40" s="3" t="n">
+        <v>17.9</v>
+      </c>
       <c r="S40" s="3" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="3" t="n"/>
-      <c r="V40" s="3" t="n"/>
-      <c r="W40" s="3" t="n"/>
+        <v>58.5</v>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="W40" s="8" t="n">
+        <v>28</v>
+      </c>
       <c r="X40" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="Y40" s="3" t="n"/>
-      <c r="Z40" s="3" t="n"/>
+        <v>13.8</v>
+      </c>
+      <c r="Y40" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Z40" s="3" t="n">
+        <v>6.2</v>
+      </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
           <t>27</t>
@@ -3296,54 +3934,76 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>234</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="E41" s="3" t="n">
+        <v>408.4</v>
+      </c>
+      <c r="D41" s="13" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E41" s="13" t="n">
         <v>12.5</v>
       </c>
-      <c r="F41" s="11" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
-      <c r="I41" s="3" t="n"/>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="N41" s="3" t="n"/>
-      <c r="O41" s="3" t="n"/>
-      <c r="P41" s="3" t="n"/>
-      <c r="Q41" s="3" t="n">
-        <v>1.3</v>
+      <c r="F41" s="13" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>8770.1</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="8" t="n">
+        <v>38.2</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>16.6</v>
+        <v>18.8</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>15</v>
+        <v>1.8</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>111.8</v>
+        <v>62.5</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="W41" s="3" t="n"/>
+        <v>10.6</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>96</v>
+      </c>
+      <c r="W41" s="8" t="n">
+        <v>658.5</v>
+      </c>
       <c r="X41" s="3" t="n">
-        <v>87</v>
+        <v>18.2</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>2.6</v>
+        <v>83</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3358,52 +4018,86 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C42" s="3" t="n"/>
-      <c r="D42" s="11" t="n">
-        <v>43.92</v>
-      </c>
-      <c r="E42" s="11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="F42" s="11" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="G42" s="3" t="n"/>
-      <c r="H42" s="8" t="n">
-        <v>42.9</v>
-      </c>
-      <c r="I42" s="3" t="n"/>
+      <c r="C42" s="3" t="n">
+        <v>340.1</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+181
+</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="J42" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L42" s="3" t="n"/>
-      <c r="M42" s="3" t="n"/>
-      <c r="N42" s="3" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2924
+991
+</t>
+        </is>
+      </c>
       <c r="O42" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P42" s="3" t="n"/>
-      <c r="Q42" s="3" t="n"/>
-      <c r="R42" s="3" t="n"/>
-      <c r="S42" s="3" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="P42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q42" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="T42" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U42" s="3" t="n"/>
-      <c r="V42" s="3" t="n"/>
+        <v>6.5</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="W42" s="3" t="n">
-        <v>1.2</v>
+        <v>15.1</v>
       </c>
       <c r="X42" s="3" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z42" s="3" t="n"/>
+        <v>81.8</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>53.7</v>
+      </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -3418,58 +4112,76 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>557.1</v>
-      </c>
-      <c r="D43" s="16" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F43" s="16" t="n">
-        <v>18</v>
+        <v>57</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <v>80.7</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>42.9</v>
+        <v>11.8</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>14.6</v>
+        <v>1.5</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="K43" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L43" s="3" t="n"/>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n"/>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="n"/>
-      <c r="Q43" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
+      <c r="K43" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="M43" s="3" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="N43" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>927.1</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q43" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>15.6</v>
+      </c>
       <c r="T43" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" s="3" t="n"/>
-      <c r="V43" s="3" t="n"/>
+        <v>58.8</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="W43" s="3" t="n">
-        <v>14.7</v>
+        <v>15.1</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>4.8</v>
+        <v>14.8</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>2.6</v>
+        <v>78</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>4</v>
+        <v>8.1</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -3485,56 +4197,80 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>228.2</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>43.92</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="F44" s="11" t="n">
-        <v>0.5</v>
+        <v>5.1</v>
+      </c>
+      <c r="D44" s="13" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="E44" s="13" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="F44" s="13" t="n">
+        <v>32.5</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H44" s="3" t="n"/>
+        <v>61</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="I44" s="3" t="n">
-        <v>14.6</v>
+        <v>2.6</v>
       </c>
       <c r="J44" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M44" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="N44" s="8" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+1272971
+</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="S44" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="K44" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="L44" s="3" t="n"/>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n"/>
-      <c r="O44" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P44" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q44" s="3" t="n"/>
-      <c r="R44" s="3" t="n"/>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n"/>
-      <c r="U44" s="3" t="n"/>
-      <c r="V44" s="3" t="n"/>
+      <c r="T44" s="3" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v>11.8</v>
+      </c>
       <c r="W44" s="3" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>18</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="X44" s="8" t="n">
+        <v>66.8</v>
       </c>
       <c r="Y44" s="3" t="n">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="Z44" s="3" t="n">
         <v>28.7</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>4</v>
       </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
@@ -3550,52 +4286,74 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>497</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>103.4</v>
-      </c>
-      <c r="E45" s="10" t="n">
+        <v>283</v>
+      </c>
+      <c r="D45" s="15" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E45" s="15" t="n">
         <v>13.3</v>
       </c>
-      <c r="F45" s="10" t="n">
-        <v>116.8</v>
-      </c>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
+      <c r="F45" s="15" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>70.8</v>
+      </c>
       <c r="I45" s="3" t="n">
-        <v>1.5</v>
+        <v>15.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
+        <v>215.2</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>28.4</v>
+      </c>
       <c r="M45" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="N45" s="3" t="n"/>
+        <v>887.1</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="O45" s="3" t="n"/>
       <c r="P45" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q45" s="3" t="n"/>
-      <c r="R45" s="3" t="n"/>
-      <c r="S45" s="3" t="n"/>
-      <c r="T45" s="3" t="n"/>
-      <c r="U45" s="3" t="n"/>
-      <c r="V45" s="3" t="n"/>
+        <v>11.6</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>979.2</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>351.1</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>18.6</v>
+      </c>
       <c r="W45" s="3" t="n">
-        <v>15.9</v>
+        <v>0.6</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>16.6</v>
+        <v>9292.6</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>72.8</v>
+        <v>7.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>4.8</v>
+        <v>28.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -3613,15 +4371,19 @@
       <c r="C46" s="3" t="n">
         <v>497</v>
       </c>
-      <c r="D46" s="12" t="n"/>
-      <c r="E46" s="10" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="F46" s="10" t="n">
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">818
+4236
+</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="15" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="G46" s="3" t="n">
         <v>10.3</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>0.1</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>11.8</v>
@@ -3633,40 +4395,47 @@
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L46" s="3" t="n"/>
-      <c r="M46" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
+        <v>1.1</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="M46" s="3" t="n"/>
+      <c r="N46" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>9.1</v>
+      </c>
       <c r="P46" s="3" t="n">
-        <v>10.6</v>
+        <v>1.8</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>22.8</v>
       </c>
-      <c r="R46" s="3" t="n"/>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n"/>
-      <c r="U46" s="3" t="n"/>
+      <c r="R46" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="V46" s="3" t="n"/>
       <c r="W46" s="3" t="n">
-        <v>9</v>
+        <v>0.1</v>
       </c>
       <c r="X46" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 14
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="Y46" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,20 +53,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,10 +155,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -167,13 +167,16 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,34 +790,44 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>582.3</v>
-      </c>
-      <c r="D4" s="15" t="n">
+        <v>582.9</v>
+      </c>
+      <c r="D4" s="11" t="n">
         <v>25.1</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="11" t="n">
         <v>13.6</v>
       </c>
-      <c r="F4" s="15" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="G4" s="15" t="n">
+      <c r="F4" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G4" s="11" t="n">
         <v>11.5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
+        <v>13.1</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>45.1</v>
+      </c>
       <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="L4" s="8" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>87</v>
+      </c>
       <c r="P4" s="3" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>25</v>
@@ -826,10 +839,14 @@
         <v>16.5</v>
       </c>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
+      <c r="U4" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>90.40000000000001</v>
+      </c>
       <c r="W4" s="3" t="n">
-        <v>0.4</v>
+        <v>17.6</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
@@ -848,37 +865,53 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>388.8</v>
-      </c>
-      <c r="D5" s="9" t="inlineStr"/>
-      <c r="E5" s="12" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="F5" s="9" t="inlineStr"/>
+        <v>288.9</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>19.1</v>
+      </c>
       <c r="G5" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>2.7</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="n">
-        <v>16.5</v>
+      <c r="L5" s="8" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>16.7</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>52</v>
@@ -889,13 +922,15 @@
       <c r="V5" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="W5" s="8" t="n">
+      <c r="W5" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="n">
+        <v>75.5</v>
+      </c>
       <c r="Z5" s="3" t="n">
         <v>6</v>
       </c>
@@ -913,32 +948,56 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2508.9</v>
-      </c>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="3" t="n">
-        <v>13.6</v>
+        <v>508.9</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>18</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
-      <c r="I6" s="3" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J6" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
+        <v>4.8</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="8" t="n">
+        <v>13.8</v>
+      </c>
       <c r="M6" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="3" t="inlineStr"/>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="3" t="inlineStr"/>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P6" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="T6" s="3" t="n">
         <v>61.9</v>
       </c>
@@ -946,16 +1005,20 @@
         <v>10.4</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W6" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W6" s="8" t="n">
         <v>16.8</v>
       </c>
-      <c r="X6" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Y6" s="3" t="inlineStr"/>
-      <c r="Z6" s="3" t="inlineStr"/>
+      <c r="X6" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>12.8</v>
+      </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -972,51 +1035,73 @@
       <c r="C7" s="3" t="n">
         <v>512.9</v>
       </c>
-      <c r="D7" s="9" t="inlineStr"/>
-      <c r="E7" s="3" t="n">
+      <c r="D7" s="11" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E7" s="11" t="n">
         <v>13.2</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>18.8</v>
+      <c r="F7" s="11" t="n">
+        <v>18.98</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N7" s="3" t="inlineStr"/>
+        <v>3.4</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="M7" s="8" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>18.8</v>
+      </c>
       <c r="O7" s="3" t="n">
-        <v>41</v>
+        <v>593</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>11.8</v>
+        <v>1.6</v>
       </c>
       <c r="Q7" s="3" t="inlineStr"/>
-      <c r="R7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="S7" s="3" t="n">
-        <v>17.9</v>
+        <v>17.4</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>59.1</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>191.8</v>
-      </c>
-      <c r="V7" s="3" t="inlineStr"/>
-      <c r="W7" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="W7" s="8" t="n">
         <v>16.6</v>
       </c>
-      <c r="X7" s="3" t="inlineStr"/>
-      <c r="Y7" s="3" t="inlineStr"/>
-      <c r="Z7" s="3" t="inlineStr"/>
+      <c r="X7" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>82.09999999999999</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -1033,17 +1118,21 @@
       <c r="C8" s="3" t="n">
         <v>229.8</v>
       </c>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F8" s="3" t="n">
+      <c r="D8" s="11" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F8" s="11" t="n">
         <v>17.7</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="11" t="n">
         <v>7.7</v>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="n">
+        <v>12.9</v>
+      </c>
       <c r="I8" s="3" t="n">
         <v>1.8</v>
       </c>
@@ -1051,7 +1140,7 @@
         <v>1.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>7.7</v>
+        <v>27.2</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>15.1</v>
@@ -1059,24 +1148,36 @@
       <c r="M8" s="3" t="n">
         <v>14.2</v>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>98</v>
+      </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q8" s="3" t="inlineStr"/>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="T8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>76</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="V8" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="W8" s="3" t="inlineStr"/>
+      <c r="W8" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="inlineStr"/>
       <c r="Z8" s="3" t="inlineStr"/>
@@ -1096,59 +1197,75 @@
       <c r="C9" s="3" t="n">
         <v>2224.9</v>
       </c>
-      <c r="D9" s="10" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="E9" s="10" t="n">
+      <c r="D9" s="11" t="n">
+        <v>118.7</v>
+      </c>
+      <c r="E9" s="11" t="n">
         <v>67.59999999999999</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="11" t="n">
         <v>93.09999999999999</v>
       </c>
-      <c r="G9" s="12" t="n">
-        <v>26.9</v>
+      <c r="G9" s="14" t="n">
+        <v>88.2</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+        <v>65.09999999999999</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>10.5</v>
+      </c>
       <c r="J9" s="3" t="n">
-        <v>116.4</v>
+        <v>16.9</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
+        <v>31.1</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>60.7</v>
+      </c>
       <c r="N9" s="3" t="n">
-        <v>14.6</v>
+        <v>86</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>459</v>
+        <v>959</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>1114</v>
+        <v>1194</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr"/>
+        <v>88.09999999999999</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>2162.6</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>22</v>
+      </c>
       <c r="V9" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="W9" s="3" t="inlineStr"/>
+        <v>959</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="X9" s="3" t="n">
-        <v>17.9</v>
+        <v>89.7</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z9" s="3" t="inlineStr"/>
+        <v>419.8</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1162,45 +1279,77 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr"/>
-      <c r="D10" s="11" t="inlineStr"/>
-      <c r="E10" s="11" t="inlineStr"/>
-      <c r="F10" s="11" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="C10" s="3" t="n">
+        <v>449</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G10" s="11" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>15.8</v>
+      </c>
       <c r="O10" s="3" t="n">
-        <v>459</v>
-      </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr"/>
+        <v>91.8</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>27</v>
+      </c>
       <c r="R10" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>62.9</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>530.1</v>
+        <v>10.6</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>94</v>
-      </c>
-      <c r="W10" s="8" t="n">
-        <v>90.8</v>
+        <v>18.8</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>89.7</v>
+        <v>17.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>415</v>
+        <v>83</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>19.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1216,53 +1365,63 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>9445</v>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>10.2</v>
+        <v>221.8</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr"/>
+        <v>12.8</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>1.4</v>
+      </c>
       <c r="J11" s="3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
+        <v>0.7</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>10.8</v>
+      </c>
       <c r="L11" s="3" t="n">
-        <v>14.7</v>
+        <v>1.2</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q11" s="3" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="P11" s="8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>19.5</v>
+      </c>
       <c r="R11" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="S11" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="T11" s="3" t="inlineStr"/>
+        <v>15.9</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>28.4</v>
+      </c>
       <c r="U11" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V11" s="8" t="n">
+      <c r="V11" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="W11" s="3" t="n">
@@ -1289,56 +1448,74 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>291.8</v>
-      </c>
-      <c r="D12" s="3" t="inlineStr"/>
-      <c r="E12" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr"/>
+        <v>229</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J12" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="8" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>92.8</v>
+      </c>
       <c r="P12" s="3" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>19.8</v>
+        <v>20.5</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>22</v>
+        <v>17.1</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>19</v>
+        <v>17.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>188.4</v>
+        <v>74.5</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>9.9</v>
+        <v>6.2</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="3" t="inlineStr"/>
-      <c r="Y12" s="3" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>240.8</v>
+      </c>
       <c r="Z12" s="3" t="inlineStr"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1353,56 +1530,78 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr"/>
+      <c r="C13" s="3" t="n">
+        <v>322</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>18.7</v>
+      </c>
       <c r="G13" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>13</v>
+        <v>9.1</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
+        <v>1.7</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>15.7</v>
+      </c>
       <c r="L13" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="R13" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q13" s="3" t="inlineStr"/>
-      <c r="R13" s="3" t="inlineStr"/>
       <c r="S13" s="3" t="n">
-        <v>17.7</v>
+        <v>1.6</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>14.9</v>
+        <v>90.5</v>
       </c>
       <c r="U13" s="3" t="n">
         <v>6.2</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X13" s="8" t="n">
-        <v>17.2</v>
+        <v>15.8</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>15.1</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z13" s="3" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
           <t>8</t>
@@ -1416,45 +1615,77 @@
           <t>9</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr"/>
-      <c r="D14" s="3" t="inlineStr"/>
-      <c r="E14" s="3" t="inlineStr"/>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="n">
-        <v>11.4</v>
+      <c r="C14" s="3" t="n">
+        <v>324</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="J14" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="K14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="n">
+        <v>26.8</v>
+      </c>
       <c r="L14" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="M14" s="3" t="inlineStr"/>
+        <v>14.4</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>13.7</v>
+      </c>
       <c r="N14" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr"/>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>18.1</v>
+      </c>
       <c r="T14" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="U14" s="3" t="inlineStr"/>
-      <c r="V14" s="3" t="inlineStr"/>
-      <c r="W14" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X14" s="3" t="inlineStr"/>
+        <v>71.90000000000001</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>17.4</v>
+      </c>
       <c r="Y14" s="3" t="n">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1469,45 +1700,75 @@
           <t>10</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
-      <c r="F15" s="3" t="inlineStr"/>
+      <c r="C15" s="3" t="n">
+        <v>307.9</v>
+      </c>
+      <c r="D15" s="12" t="inlineStr"/>
+      <c r="E15" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>78.3</v>
+      </c>
       <c r="G15" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="H15" s="3" t="inlineStr"/>
-      <c r="I15" s="3" t="inlineStr"/>
+        <v>11.2</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>1.2</v>
+      </c>
       <c r="J15" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="M15" s="3" t="n">
-        <v>13.7</v>
+        <v>148.1</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="O15" s="3" t="inlineStr"/>
+        <v>15.5</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>96.8</v>
+      </c>
       <c r="P15" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q15" s="3" t="inlineStr"/>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="T15" s="3" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="U15" s="3" t="inlineStr"/>
-      <c r="V15" s="3" t="inlineStr"/>
+        <v>73</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>16.6</v>
+      </c>
       <c r="W15" s="3" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="X15" s="3" t="inlineStr"/>
-      <c r="Y15" s="3" t="inlineStr"/>
+        <v>15.7</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>92</v>
+      </c>
       <c r="Z15" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1522,48 +1783,78 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="11" t="inlineStr"/>
-      <c r="E16" s="11" t="inlineStr"/>
-      <c r="F16" s="11" t="inlineStr"/>
-      <c r="G16" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="n">
+        <v>1972.2</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>649.4</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>6.9</v>
+      </c>
       <c r="K16" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
+        <v>46.8</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>191.2</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>69.40000000000001</v>
+      </c>
       <c r="N16" s="3" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="O16" s="3" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q16" s="3" t="n">
         <v>96.90000000000001</v>
       </c>
-      <c r="P16" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q16" s="3" t="inlineStr"/>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>88.40000000000001</v>
+      </c>
       <c r="T16" s="3" t="n">
-        <v>73</v>
-      </c>
-      <c r="U16" s="3" t="inlineStr"/>
+        <v>164.8</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>24.8</v>
+      </c>
       <c r="V16" s="3" t="n">
-        <v>16.6</v>
+        <v>84.5</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X16" s="3" t="inlineStr"/>
+        <v>180.6</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>85.09999999999999</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="Z16" s="3" t="inlineStr"/>
+        <v>488.8</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -1578,74 +1869,76 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>1972.2</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="F17" s="12" t="n">
+        <v>225</v>
+      </c>
+      <c r="D17" s="16" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F17" s="14" t="n">
         <v>91.09999999999999</v>
       </c>
-      <c r="G17" s="15" t="n">
-        <v>47.4</v>
+      <c r="G17" s="3" t="n">
+        <v>9.5</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>4.4</v>
+        <v>12.9</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>1.2</v>
+      </c>
+      <c r="J17" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>46.8</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="M17" s="8" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="N17" s="8" t="n">
-        <v>16464.6</v>
-      </c>
-      <c r="O17" s="3" t="inlineStr"/>
+        <v>14.6</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>92.90000000000001</v>
+      </c>
       <c r="P17" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="S17" s="8" t="n">
-        <v>88</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>324.5</v>
+        <v>18.9</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>24.2</v>
+        <v>9</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="W17" s="8" t="n">
-        <v>718.6</v>
+        <v>16.9</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>15.7</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>86.09999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>2420.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>2</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1661,54 +1954,74 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>225</v>
-      </c>
-      <c r="D18" s="8" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="9" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="8" t="n">
-        <v>12.9</v>
+        <v>428.8</v>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1.2</v>
+        <v>10.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="K18" s="3" t="inlineStr"/>
+        <v>3.6</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="L18" s="3" t="n">
-        <v>34.6</v>
+        <v>14</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N18" s="3" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="O18" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="3" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>21.8</v>
+      </c>
       <c r="R18" s="3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>416.1</v>
+        <v>18.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="U18" s="3" t="inlineStr"/>
+        <v>69.09999999999999</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="V18" s="3" t="n">
         <v>16.9</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="X18" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>81.8</v>
+      </c>
       <c r="Z18" s="3" t="n">
         <v>2</v>
       </c>
@@ -1726,54 +2039,74 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>428.5</v>
-      </c>
-      <c r="D19" s="3" t="n">
+        <v>840.6</v>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q19" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="E19" s="3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F19" s="9" t="inlineStr"/>
-      <c r="G19" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>17</v>
+      </c>
       <c r="T19" s="3" t="n">
-        <v>169.1</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>8</v>
+        <v>54</v>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v>14.4</v>
       </c>
       <c r="V19" s="3" t="inlineStr"/>
-      <c r="W19" s="3" t="inlineStr"/>
-      <c r="X19" s="3" t="inlineStr"/>
+      <c r="W19" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="Y19" s="3" t="n">
         <v>81</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>4</v>
+        <v>27.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -1789,47 +2122,77 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2440.6</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="9" t="inlineStr"/>
-      <c r="G20" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
+        <v>153.1</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G20" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="O20" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y20" s="3" t="n">
         <v>92</v>
       </c>
-      <c r="P20" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="3" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V20" s="3" t="inlineStr"/>
-      <c r="W20" s="3" t="inlineStr"/>
-      <c r="X20" s="3" t="inlineStr"/>
-      <c r="Y20" s="3" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="Z20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="n">
+        <v>1.6</v>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -1844,45 +2207,77 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>153.1</v>
+        <v>261.7</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="9" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
+        <v>20.6</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>11.9</v>
+      </c>
       <c r="K21" s="3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
+        <v>10.9</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O21" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr"/>
+        <v>90.8</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="T21" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="U21" s="3" t="inlineStr"/>
-      <c r="V21" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V21" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="W21" s="3" t="inlineStr"/>
-      <c r="X21" s="3" t="inlineStr"/>
+      <c r="W21" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y21" s="3" t="n">
-        <v>192</v>
-      </c>
-      <c r="Z21" s="3" t="inlineStr"/>
+        <v>880.9</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>2.8</v>
+      </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -1897,52 +2292,74 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1261.7</v>
+        <v>123.3</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E22" s="3" t="inlineStr"/>
-      <c r="F22" s="9" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="I22" s="3" t="inlineStr"/>
+        <v>24.9</v>
+      </c>
+      <c r="E22" s="14" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="J22" s="3" t="n">
-        <v>9.9</v>
+        <v>11.9</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="O22" s="3" t="n">
-        <v>90.8</v>
-      </c>
-      <c r="P22" s="3" t="inlineStr"/>
+        <v>911</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1.8</v>
+      </c>
       <c r="Q22" s="3" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="n">
-        <v>18.9</v>
+        <v>20.4</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="S22" s="8" t="n">
+        <v>17.8</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>74</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>16.6</v>
+        <v>6.2</v>
       </c>
       <c r="V22" s="3" t="inlineStr"/>
-      <c r="W22" s="3" t="inlineStr"/>
-      <c r="X22" s="3" t="inlineStr"/>
+      <c r="W22" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Y22" s="3" t="n">
-        <v>870.9</v>
+        <v>94.5</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -1958,58 +2375,74 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>123.3</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>120.6</v>
-      </c>
-      <c r="E23" s="11" t="inlineStr"/>
-      <c r="F23" s="10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
+        <v>1971.2</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>11153.1</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>940.8</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>43.1</v>
+      </c>
       <c r="H23" s="3" t="n">
-        <v>93.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr"/>
+        <v>80.8</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
       <c r="K23" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="n">
-        <v>1.6</v>
-      </c>
+        <v>38.2</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>122.1</v>
+      </c>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>91.8</v>
+        <v>14.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>11.8</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>120.4</v>
-      </c>
-      <c r="R23" s="3" t="inlineStr"/>
+        <v>109</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>88.8</v>
+      </c>
       <c r="S23" s="3" t="n">
-        <v>117.8</v>
+        <v>90</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>74</v>
+        <v>347.9</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V23" s="3" t="inlineStr"/>
-      <c r="W23" s="3" t="inlineStr"/>
-      <c r="X23" s="3" t="inlineStr"/>
+        <v>40.6</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v>918.9</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>911.8</v>
+      </c>
       <c r="Y23" s="3" t="n">
-        <v>94.90000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>1.8</v>
+        <v>113.8</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2025,74 +2458,76 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1983.2</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>113</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="G24" s="15" t="n">
-        <v>43.7</v>
+        <v>215.4</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F24" s="16" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="G24" s="11" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>644.4</v>
+        <v>69.8</v>
       </c>
       <c r="I24" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="Z24" s="3" t="n">
         <v>2.8</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>332.1</v>
-      </c>
-      <c r="L24" s="8" t="n">
-        <v>7162.1</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="N24" s="8" t="n">
-        <v>461.8</v>
-      </c>
-      <c r="O24" s="3" t="inlineStr"/>
-      <c r="P24" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q24" s="8" t="n">
-        <v>9</v>
-      </c>
-      <c r="R24" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="T24" s="3" t="n">
-        <v>347.9</v>
-      </c>
-      <c r="U24" s="3" t="n">
-        <v>406.4</v>
-      </c>
-      <c r="V24" s="3" t="n">
-        <v>91.8</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>94.2</v>
-      </c>
-      <c r="Y24" s="3" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="Z24" s="3" t="n">
-        <v>198.4</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2108,56 +2543,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>235.4</v>
-      </c>
-      <c r="D25" s="15" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F25" s="15" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="G25" s="15" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H25" s="3" t="n">
+        <v>490.4</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M25" s="8" t="n">
+        <v>849.2</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>910.8</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="W25" s="8" t="n">
         <v>12.9</v>
       </c>
-      <c r="I25" s="3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="R25" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S25" s="3" t="n">
+      <c r="X25" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="T25" s="3" t="inlineStr"/>
-      <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="W25" s="3" t="inlineStr"/>
-      <c r="X25" s="3" t="inlineStr"/>
-      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Y25" s="3" t="n">
+        <v>94</v>
+      </c>
       <c r="Z25" s="3" t="n">
         <v>2.8</v>
       </c>
@@ -2175,53 +2628,77 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>490.4</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
+        <v>281.8</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>8.9</v>
+      </c>
       <c r="H26" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="L26" s="8" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>73</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="V26" s="3" t="n">
         <v>12.9</v>
       </c>
-      <c r="I26" s="3" t="inlineStr"/>
-      <c r="J26" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
-      <c r="O26" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="R26" s="3" t="inlineStr"/>
-      <c r="S26" s="8" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="T26" s="3" t="inlineStr"/>
-      <c r="U26" s="3" t="inlineStr"/>
-      <c r="V26" s="3" t="n">
-        <v>16.6</v>
-      </c>
       <c r="W26" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="X26" s="3" t="inlineStr"/>
-      <c r="Y26" s="3" t="inlineStr"/>
-      <c r="Z26" s="3" t="inlineStr"/>
+        <v>16.2</v>
+      </c>
+      <c r="X26" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
           <t>17</t>
@@ -2235,50 +2712,78 @@
           <t>18</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
-      <c r="D27" s="9" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="n">
+        <v>305.9</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>14.9</v>
+      </c>
       <c r="I27" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr"/>
+        <v>2.4</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>21.9</v>
+      </c>
       <c r="K27" s="3" t="n">
-        <v>3.9</v>
+        <v>10.8</v>
       </c>
       <c r="L27" s="8" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="M27" s="3" t="inlineStr"/>
+        <v>15.4</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>14.8</v>
+      </c>
       <c r="N27" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S27" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z27" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="O27" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="P27" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q27" s="3" t="inlineStr"/>
-      <c r="R27" s="3" t="inlineStr"/>
-      <c r="S27" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T27" s="3" t="n">
-        <v>173</v>
-      </c>
-      <c r="U27" s="3" t="inlineStr"/>
-      <c r="V27" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="W27" s="3" t="inlineStr"/>
-      <c r="X27" s="3" t="inlineStr"/>
-      <c r="Y27" s="3" t="inlineStr"/>
-      <c r="Z27" s="3" t="inlineStr"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
           <t>18</t>
@@ -2292,50 +2797,78 @@
           <t>19</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
-      <c r="D28" s="9" t="inlineStr"/>
-      <c r="E28" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="n">
+        <v>2023.9</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="I28" s="3" t="n">
-        <v>24.2</v>
+        <v>0.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="inlineStr"/>
+        <v>21.9</v>
+      </c>
+      <c r="K28" s="8" t="n">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>14.2</v>
+      </c>
       <c r="N28" s="3" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q28" s="3" t="inlineStr"/>
-      <c r="R28" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>17</v>
+      </c>
       <c r="S28" s="3" t="n">
-        <v>19.9</v>
+        <v>17.2</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U28" s="3" t="inlineStr"/>
-      <c r="V28" s="3" t="inlineStr"/>
-      <c r="W28" s="3" t="inlineStr"/>
-      <c r="X28" s="3" t="inlineStr"/>
-      <c r="Y28" s="3" t="inlineStr"/>
-      <c r="Z28" s="3" t="inlineStr"/>
+        <v>72.8</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>83.8</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
           <t>19</t>
@@ -2350,47 +2883,77 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>305.9</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E29" s="3" t="inlineStr"/>
-      <c r="F29" s="3" t="inlineStr"/>
+        <v>289.8</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>17.8</v>
+      </c>
       <c r="G29" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>82.8</v>
+        <v>2.1</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="J29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="K29" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="M29" s="3" t="n">
+        <v>14.4</v>
+      </c>
       <c r="N29" s="3" t="n">
-        <v>1.8</v>
+        <v>16.5</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>195</v>
-      </c>
-      <c r="P29" s="3" t="inlineStr"/>
-      <c r="Q29" s="3" t="inlineStr"/>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="Q29" s="8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="T29" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="U29" s="3" t="inlineStr"/>
-      <c r="V29" s="3" t="inlineStr"/>
-      <c r="W29" s="3" t="inlineStr"/>
-      <c r="X29" s="3" t="inlineStr"/>
-      <c r="Y29" s="3" t="inlineStr"/>
-      <c r="Z29" s="3" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="Y29" s="3" t="n">
+        <v>85</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>3.2</v>
+      </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
           <t>20</t>
@@ -2405,51 +2968,77 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>289.8</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>121.9</v>
-      </c>
-      <c r="E30" s="11" t="inlineStr"/>
-      <c r="F30" s="11" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
+        <v>1682.9</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>43.7</v>
+      </c>
       <c r="H30" s="3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>456.6</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>20021.4</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>561.9</v>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>394.6</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="X30" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="I30" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="3" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="O30" s="3" t="n">
-        <v>95</v>
-      </c>
-      <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="3" t="inlineStr"/>
-      <c r="R30" s="3" t="inlineStr"/>
-      <c r="S30" s="3" t="inlineStr"/>
-      <c r="T30" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="U30" s="3" t="inlineStr"/>
-      <c r="V30" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W30" s="3" t="inlineStr"/>
-      <c r="X30" s="3" t="n">
-        <v>182200.9</v>
-      </c>
-      <c r="Y30" s="3" t="inlineStr"/>
-      <c r="Z30" s="3" t="inlineStr"/>
+      <c r="Y30" s="3" t="n">
+        <v>441.8</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>112.2</v>
+      </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -2464,70 +3053,76 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1609.9</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>36</v>
-      </c>
-      <c r="F31" s="12" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>4.3</v>
+        <v>322</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="F31" s="16" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>86.59999999999999</v>
+        <v>22.8</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>9.4</v>
+        <v>1.8</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
+        <v>456.6</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="O31" s="3" t="n">
-        <v>42034.4</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>5.4</v>
+        <v>1</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>21</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>18.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>361.1</v>
+        <v>561.9</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>34.6</v>
+        <v>6.9</v>
       </c>
       <c r="V31" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y31" s="3" t="n">
         <v>88.8</v>
       </c>
-      <c r="W31" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>88.2</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>9491</v>
-      </c>
       <c r="Z31" s="3" t="n">
-        <v>7.1</v>
+        <v>941.6</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -2543,59 +3138,77 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D32" s="15" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E32" s="15" t="n">
+        <v>482.8</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="E32" s="11" t="n">
         <v>13.7</v>
       </c>
-      <c r="F32" s="15" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="G32" s="15" t="n">
+      <c r="F32" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J32" s="3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H32" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="3" t="inlineStr"/>
+      <c r="K32" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>14.9</v>
+      </c>
       <c r="N32" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="O32" s="3" t="inlineStr"/>
+        <v>16.8</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>895</v>
+      </c>
       <c r="P32" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q32" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="Q32" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="R32" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="S32" s="3" t="inlineStr"/>
-      <c r="T32" s="3" t="inlineStr"/>
-      <c r="U32" s="8" t="n">
-        <v>81</v>
+      <c r="R32" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>901.1</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>2.2</v>
       </c>
       <c r="V32" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="W32" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="X32" s="3" t="inlineStr"/>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="inlineStr"/>
+        <v>14.9</v>
+      </c>
+      <c r="W32" s="8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>8</v>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -2609,57 +3222,77 @@
           <t>22</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr"/>
-      <c r="D33" s="9" t="inlineStr"/>
-      <c r="E33" s="3" t="inlineStr"/>
-      <c r="F33" s="9" t="inlineStr"/>
-      <c r="G33" s="3" t="n">
-        <v>8.9</v>
+      <c r="C33" s="3" t="n">
+        <v>482.8</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="G33" s="8" t="n">
+        <v>11.7</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>12.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I33" s="3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>93</v>
+      </c>
+      <c r="P33" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="J33" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="O33" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="P33" s="3" t="inlineStr"/>
-      <c r="Q33" s="8" t="n">
-        <v>17</v>
+      <c r="Q33" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="R33" s="3" t="n">
-        <v>158.1</v>
-      </c>
-      <c r="S33" s="8" t="n">
-        <v>11.8</v>
+        <v>16.8</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>12</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="U33" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V33" s="3" t="inlineStr"/>
-      <c r="W33" s="3" t="inlineStr"/>
-      <c r="X33" s="3" t="inlineStr"/>
+        <v>31.9</v>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W33" s="8" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="Y33" s="3" t="n">
-        <v>195</v>
+        <v>71.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -2674,49 +3307,75 @@
           <t>23</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr"/>
-      <c r="D34" s="9" t="inlineStr"/>
-      <c r="E34" s="8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>17.9</v>
+      <c r="C34" s="3" t="n">
+        <v>492.8</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>18.9</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>19.7</v>
+        <v>12.6</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>88.59999999999999</v>
-      </c>
-      <c r="I34" s="3" t="inlineStr"/>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>23.1</v>
+      </c>
       <c r="J34" s="3" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
+        <v>3.9</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="M34" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="O34" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="inlineStr"/>
-      <c r="R34" s="3" t="inlineStr"/>
-      <c r="S34" s="3" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="T34" s="3" t="n">
-        <v>121.9</v>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V34" s="3" t="inlineStr"/>
-      <c r="W34" s="3" t="inlineStr"/>
+        <v>26.8</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>16.8</v>
+      </c>
       <c r="X34" s="3" t="inlineStr"/>
       <c r="Y34" s="3" t="n">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>4.8</v>
+        <v>89.2</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -2731,47 +3390,75 @@
           <t>24</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr"/>
-      <c r="D35" s="9" t="inlineStr"/>
-      <c r="E35" s="8" t="n">
-        <v>11.5</v>
+      <c r="C35" s="3" t="n">
+        <v>172.6</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>13.6</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>19.3</v>
+        <v>13.3</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>12.6</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr"/>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J35" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr"/>
+      <c r="L35" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="M35" s="8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>1.7</v>
+      </c>
       <c r="O35" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr"/>
+        <v>9180</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="T35" s="3" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U35" s="3" t="inlineStr"/>
-      <c r="V35" s="3" t="inlineStr"/>
-      <c r="W35" s="3" t="inlineStr"/>
+        <v>600.8</v>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="X35" s="3" t="inlineStr"/>
-      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Y35" s="3" t="n">
+        <v>75.5</v>
+      </c>
       <c r="Z35" s="3" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -2786,45 +3473,73 @@
           <t>25</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr"/>
-      <c r="D36" s="9" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="n">
+      <c r="C36" s="3" t="n">
+        <v>498.3</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F36" s="11" t="n">
         <v>19.1</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G36" s="11" t="n">
         <v>10.3</v>
       </c>
       <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="n">
+        <v>2.3</v>
+      </c>
       <c r="J36" s="3" t="n">
         <v>4</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="N36" s="3" t="inlineStr"/>
-      <c r="O36" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="M36" s="3" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>91</v>
+      </c>
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="3" t="inlineStr"/>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr"/>
+      <c r="Q36" s="8" t="n">
+        <v>129.2</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S36" s="8" t="n">
+        <v>71</v>
+      </c>
       <c r="T36" s="3" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="U36" s="3" t="inlineStr"/>
+        <v>552.1</v>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v>12.8</v>
+      </c>
       <c r="V36" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="W36" s="3" t="inlineStr"/>
-      <c r="X36" s="3" t="inlineStr"/>
-      <c r="Y36" s="3" t="inlineStr"/>
+      <c r="W36" s="3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>79.8</v>
+      </c>
       <c r="Z36" s="3" t="n">
         <v>4.5</v>
       </c>
@@ -2842,61 +3557,73 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1182.8</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>112.2</v>
-      </c>
-      <c r="E37" s="11" t="inlineStr"/>
-      <c r="F37" s="10" t="n">
-        <v>928.6</v>
+        <v>2122</v>
+      </c>
+      <c r="D37" s="16" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="F37" s="16" t="n">
+        <v>22.6</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
+        <v>22.9</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>4</v>
+      </c>
       <c r="I37" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="3" t="inlineStr"/>
+        <v>110.8</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>122.9</v>
+      </c>
       <c r="L37" s="3" t="n">
-        <v>1.3</v>
+        <v>29.1</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N37" s="3" t="inlineStr"/>
+        <v>8012</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>19.1</v>
+      </c>
       <c r="O37" s="3" t="n">
-        <v>9449</v>
+        <v>449</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Q37" s="3" t="inlineStr"/>
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Q37" s="3" t="n">
+        <v>113.4</v>
+      </c>
       <c r="R37" s="3" t="n">
-        <v>81.8</v>
+        <v>1</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>284.8</v>
+        <v>84.8</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>312.4</v>
+        <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>24.8</v>
+        <v>25.8</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>1291</v>
+        <v>21</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>50.4</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>85.2</v>
+        <v>82</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>909.2</v>
+        <v>940.2</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>128.1</v>
@@ -2917,51 +3644,75 @@
       <c r="C38" s="3" t="n">
         <v>9438.6</v>
       </c>
-      <c r="D38" s="11" t="inlineStr"/>
-      <c r="E38" s="3" t="inlineStr"/>
-      <c r="F38" s="12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="G38" s="3" t="inlineStr"/>
+      <c r="D38" s="16" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G38" s="11" t="n">
+        <v>10.5</v>
+      </c>
       <c r="H38" s="3" t="n">
-        <v>12.8</v>
+        <v>12.3</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="n">
-        <v>45.4</v>
+        <v>23.2</v>
+      </c>
+      <c r="K38" s="8" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L38" s="8" t="n">
+        <v>15.1</v>
       </c>
       <c r="M38" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="N38" s="3" t="inlineStr"/>
+      <c r="N38" s="8" t="n">
+        <v>52.1</v>
+      </c>
       <c r="O38" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="Q38" s="3" t="n">
+        <v>22.7</v>
+      </c>
       <c r="R38" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S38" s="3" t="inlineStr"/>
-      <c r="T38" s="3" t="inlineStr"/>
-      <c r="U38" s="3" t="inlineStr"/>
+        <v>17.4</v>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>313.4</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>11</v>
+      </c>
       <c r="V38" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>464.1</v>
-      </c>
-      <c r="X38" s="3" t="inlineStr"/>
-      <c r="Y38" s="3" t="inlineStr"/>
-      <c r="Z38" s="3" t="inlineStr"/>
+        <v>16.1</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>940.2</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -2976,55 +3727,77 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1395.3</v>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="F39" s="15" t="n">
-        <v>18.2</v>
+        <v>395</v>
+      </c>
+      <c r="D39" s="14" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="E39" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="G39" s="8" t="n">
         <v>11.8</v>
       </c>
-      <c r="H39" s="8" t="n">
-        <v>12.8</v>
+      <c r="H39" s="3" t="n">
+        <v>12.3</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
+        <v>12.1</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M39" s="8" t="n">
+        <v>150.1</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>18.9</v>
+      </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y39" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="Q39" s="3" t="inlineStr"/>
-      <c r="R39" s="3" t="inlineStr"/>
-      <c r="S39" s="3" t="inlineStr"/>
-      <c r="T39" s="3" t="n">
-        <v>520.8</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="W39" s="3" t="inlineStr"/>
-      <c r="X39" s="3" t="inlineStr"/>
-      <c r="Y39" s="3" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="Z39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="n">
+        <v>16.4</v>
+      </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
           <t>26</t>
@@ -3039,44 +3812,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>4034.4</v>
-      </c>
-      <c r="D40" s="9" t="inlineStr"/>
-      <c r="E40" s="3" t="inlineStr"/>
-      <c r="F40" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr"/>
+        <v>2942.1</v>
+      </c>
+      <c r="D40" s="8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E40" s="14" t="n">
+        <v>92</v>
+      </c>
+      <c r="F40" s="14" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="G40" s="8" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>11.5</v>
+      </c>
       <c r="I40" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K40" s="3" t="inlineStr"/>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
+        <v>3.5</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr"/>
+      <c r="K40" s="3" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="L40" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="M40" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="N40" s="8" t="n">
+        <v>38.9</v>
+      </c>
       <c r="O40" s="3" t="n">
-        <v>89</v>
-      </c>
-      <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="3" t="inlineStr"/>
-      <c r="R40" s="3" t="inlineStr"/>
-      <c r="S40" s="3" t="inlineStr"/>
-      <c r="T40" s="3" t="inlineStr"/>
-      <c r="U40" s="8" t="n">
+        <v>91</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="U40" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V40" s="8" t="n">
+      <c r="V40" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="W40" s="3" t="inlineStr"/>
-      <c r="X40" s="3" t="inlineStr"/>
-      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="W40" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="Y40" s="3" t="n">
+        <v>72</v>
+      </c>
       <c r="Z40" s="3" t="n">
-        <v>16.2</v>
+        <v>6.2</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3092,52 +3895,74 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>340.1</v>
-      </c>
-      <c r="D41" s="9" t="inlineStr"/>
-      <c r="E41" s="3" t="inlineStr"/>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="n">
-        <v>2.2</v>
+        <v>408.4</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G41" s="11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="I41" s="8" t="n">
+        <v>11.1</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K41" s="3" t="inlineStr"/>
+        <v>4.7</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L41" s="3" t="n">
-        <v>69.8</v>
+        <v>14.8</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N41" s="3" t="inlineStr"/>
+        <v>13.6</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>19.2</v>
+      </c>
       <c r="O41" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="inlineStr"/>
-      <c r="S41" s="3" t="inlineStr"/>
-      <c r="T41" s="3" t="inlineStr"/>
+      <c r="Q41" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>68.5</v>
+      </c>
       <c r="U41" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="W41" s="3" t="n">
-        <v>16.8</v>
+        <v>12</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="W41" s="8" t="n">
+        <v>72</v>
       </c>
       <c r="X41" s="3" t="inlineStr"/>
       <c r="Y41" s="3" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3153,50 +3978,64 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>1337</v>
-      </c>
-      <c r="D42" s="9" t="inlineStr"/>
-      <c r="E42" s="3" t="inlineStr"/>
-      <c r="F42" s="3" t="inlineStr"/>
+        <v>349.1</v>
+      </c>
+      <c r="D42" s="12" t="inlineStr"/>
+      <c r="E42" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F42" s="14" t="n">
+        <v>1.8</v>
+      </c>
       <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="n">
-        <v>1.7</v>
-      </c>
+      <c r="H42" s="8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I42" s="3" t="inlineStr"/>
       <c r="J42" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K42" s="3" t="inlineStr"/>
-      <c r="L42" s="3" t="n">
-        <v>10.4</v>
-      </c>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3" t="inlineStr"/>
       <c r="M42" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="N42" s="3" t="inlineStr"/>
+        <v>1.8</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>14.6</v>
+      </c>
       <c r="O42" s="3" t="n">
-        <v>82</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q42" s="3" t="inlineStr"/>
-      <c r="R42" s="3" t="inlineStr"/>
-      <c r="S42" s="3" t="inlineStr"/>
-      <c r="T42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>289.5</v>
+      </c>
       <c r="U42" s="3" t="n">
-        <v>142.4</v>
-      </c>
-      <c r="V42" s="3" t="inlineStr"/>
+        <v>10.4</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>18.2</v>
+      </c>
       <c r="W42" s="3" t="n">
         <v>16.8</v>
       </c>
       <c r="X42" s="3" t="inlineStr"/>
       <c r="Y42" s="3" t="n">
-        <v>81.8</v>
+        <v>87</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>98.7</v>
+        <v>2.6</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -3212,52 +4051,66 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>1653.1</v>
-      </c>
-      <c r="D43" s="9" t="inlineStr"/>
+        <v>517</v>
+      </c>
+      <c r="D43" s="12" t="inlineStr"/>
       <c r="E43" s="3" t="inlineStr"/>
       <c r="F43" s="3" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr"/>
+      <c r="H43" s="8" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I43" s="8" t="n">
+        <v>18.8</v>
+      </c>
       <c r="J43" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K43" s="3" t="inlineStr"/>
+        <v>21.1</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L43" s="3" t="n">
-        <v>1.4</v>
+        <v>16.2</v>
       </c>
       <c r="M43" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="N43" s="3" t="inlineStr"/>
+        <v>4.4</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="O43" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
+        <v>82</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q43" s="3" t="n">
+        <v>22.2</v>
+      </c>
       <c r="R43" s="3" t="n">
-        <v>18.7</v>
+        <v>1.6</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>12.9</v>
+        <v>15.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>959.3</v>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="V43" s="3" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="n">
+        <v>17.5</v>
+      </c>
       <c r="W43" s="3" t="inlineStr"/>
-      <c r="X43" s="3" t="inlineStr"/>
+      <c r="X43" s="3" t="n">
+        <v>16.2</v>
+      </c>
       <c r="Y43" s="3" t="n">
-        <v>78</v>
+        <v>81.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>85</v>
+        <v>3.7</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -3273,18 +4126,24 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>22830.1</v>
-      </c>
-      <c r="D44" s="12" t="n">
-        <v>91.7</v>
-      </c>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="n">
+        <v>653.1</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F44" s="11" t="n">
         <v>18</v>
       </c>
       <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>2.6</v>
+      </c>
       <c r="J44" s="3" t="n">
         <v>5</v>
       </c>
@@ -3292,7 +4151,7 @@
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>1.4</v>
+        <v>13.6</v>
       </c>
       <c r="M44" s="3" t="n">
         <v>12.6</v>
@@ -3301,33 +4160,29 @@
       <c r="O44" s="3" t="n">
         <v>91</v>
       </c>
-      <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="n">
-        <v>18.7</v>
+      <c r="P44" s="3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="Q44" s="3" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="R44" s="8" t="n">
+        <v>68.09999999999999</v>
       </c>
       <c r="S44" s="3" t="n">
-        <v>12.9</v>
+        <v>13.9</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>959.3</v>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="n">
-        <v>95.8</v>
-      </c>
-      <c r="X44" s="3" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>78</v>
-      </c>
-      <c r="Z44" s="3" t="n">
-        <v>28.7</v>
-      </c>
+        <v>59.5</v>
+      </c>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -3342,54 +4197,70 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>22830.1</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>191.7</v>
-      </c>
-      <c r="E45" s="11" t="inlineStr"/>
-      <c r="F45" s="11" t="inlineStr"/>
+        <v>2283</v>
+      </c>
+      <c r="D45" s="16" t="n">
+        <v>198.5</v>
+      </c>
+      <c r="E45" s="13" t="inlineStr"/>
+      <c r="F45" s="16" t="n">
+        <v>110.8</v>
+      </c>
       <c r="G45" s="3" t="n">
-        <v>62</v>
+        <v>2</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>10.8</v>
+        <v>128.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>15.2</v>
+        <v>13.2</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>126.2</v>
+        <v>26.2</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
+        <v>10.1</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="M45" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>91.8</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>240.9</v>
-      </c>
-      <c r="P45" s="3" t="inlineStr"/>
-      <c r="Q45" s="3" t="inlineStr"/>
+        <v>290.9</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="Q45" s="3" t="n">
+        <v>137</v>
+      </c>
       <c r="R45" s="3" t="inlineStr"/>
       <c r="S45" s="3" t="n">
-        <v>98.2</v>
-      </c>
-      <c r="T45" s="3" t="inlineStr"/>
+        <v>99.8</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>381</v>
+      </c>
       <c r="U45" s="3" t="inlineStr"/>
       <c r="V45" s="3" t="n">
         <v>111.8</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>95.8</v>
+        <v>220.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="Y45" s="3" t="inlineStr"/>
+        <v>89.59999999999999</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>4648.4</v>
+      </c>
       <c r="Z45" s="3" t="n">
-        <v>28.7</v>
+        <v>28.1</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -3405,57 +4276,69 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>29497</v>
-      </c>
-      <c r="D46" s="10" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E46" s="12" t="n">
+        <v>498</v>
+      </c>
+      <c r="D46" s="16" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G46" s="11" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J46" s="3" t="n">
         <v>4.4</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="G46" s="8" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H46" s="8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>44.4</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
       <c r="L46" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="3" t="inlineStr"/>
+      <c r="M46" s="8" t="n">
+        <v>13.8</v>
+      </c>
       <c r="N46" s="3" t="inlineStr"/>
-      <c r="O46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="n">
+        <v>201.1</v>
+      </c>
       <c r="P46" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q46" s="3" t="inlineStr"/>
+        <v>19.4</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>22.8</v>
+      </c>
       <c r="R46" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>16.2</v>
       </c>
-      <c r="T46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="n">
+        <v>58.5</v>
+      </c>
       <c r="U46" s="3" t="inlineStr"/>
       <c r="V46" s="3" t="n">
-        <v>212.6</v>
-      </c>
-      <c r="W46" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="W46" s="8" t="n">
         <v>15.9</v>
       </c>
       <c r="X46" s="3" t="inlineStr"/>
-      <c r="Y46" s="3" t="inlineStr"/>
-      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>4.8</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
+++ b/results/05_transient_transcription_output/601/601_196705_SF.JPG_stage_2ndrecheck_temp_thresholds.xlsx
@@ -47,6 +47,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -55,12 +61,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -155,13 +155,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,13 +170,22 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -790,38 +799,40 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>582.9</v>
-      </c>
-      <c r="D4" s="11" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="E4" s="11" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F4" s="11" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="G4" s="11" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="D4" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="F4" s="12" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="G4" s="12" t="n">
         <v>11.5</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>13.1</v>
+        <v>1.3</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
+        <v>2.8</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="K4" s="3" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="L4" s="8" t="n">
-        <v>11.2</v>
+        <v>0.2</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>14.7</v>
       </c>
       <c r="M4" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>1.9</v>
+      <c r="N4" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>87</v>
@@ -838,15 +849,17 @@
       <c r="S4" s="3" t="n">
         <v>16.5</v>
       </c>
-      <c r="T4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="n">
+        <v>59</v>
+      </c>
       <c r="U4" s="8" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>90.40000000000001</v>
+        <v>15.9</v>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v>21.7</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>17.6</v>
+        <v>10.1</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="inlineStr"/>
@@ -865,59 +878,61 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>288.9</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="E5" s="11" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="E5" s="12" t="n">
         <v>14.2</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="12" t="n">
         <v>19.1</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="H5" s="8" t="n">
-        <v>12.3</v>
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="I5" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="M5" s="8" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="P5" s="3" t="n">
         <v>1.9</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="8" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="M5" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>92</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>19.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="S5" s="8" t="n">
-        <v>16.7</v>
+        <v>17.9</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>52</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>15.2</v>
+        <v>1.5</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>20.7</v>
@@ -929,7 +944,7 @@
         <v>18.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>75.5</v>
+        <v>175.5</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>6</v>
@@ -948,76 +963,76 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>508.9</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="E6" s="11" t="n">
+        <v>208.9</v>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>12.8</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>18</v>
+      <c r="F6" s="12" t="n">
+        <v>18.9</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H6" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H6" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="8" t="n">
-        <v>13.8</v>
+      <c r="L6" s="3" t="n">
+        <v>43.4</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>13</v>
+        <v>13.9</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>1.9</v>
+        <v>4.8</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>92</v>
+        <v>19.8</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>25.6</v>
+        <v>23.6</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>1.7</v>
+        <v>17.8</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>61.9</v>
+        <v>61.5</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>10.4</v>
       </c>
-      <c r="V6" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="W6" s="8" t="n">
+      <c r="V6" s="17" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="W6" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="X6" s="8" t="n">
-        <v>18.1</v>
+      <c r="X6" s="3" t="n">
+        <v>18.3</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>12.8</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1035,19 +1050,19 @@
       <c r="C7" s="3" t="n">
         <v>512.9</v>
       </c>
-      <c r="D7" s="11" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>18.98</v>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="D7" s="12" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G7" s="12" t="n">
         <v>10.7</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="8" t="n">
         <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
@@ -1057,50 +1072,50 @@
         <v>3.4</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>14.3</v>
       </c>
-      <c r="M7" s="8" t="n">
-        <v>23.6</v>
+      <c r="M7" s="3" t="n">
+        <v>13.6</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>593</v>
+        <v>1.6</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q7" s="3" t="inlineStr"/>
+        <v>18.8</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>29.5</v>
+      </c>
       <c r="R7" s="3" t="n">
-        <v>17.6</v>
+        <v>17.1</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>17.4</v>
+        <v>12.4</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>59.1</v>
       </c>
-      <c r="U7" s="8" t="n">
+      <c r="U7" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>18.7</v>
+        <v>10.1</v>
       </c>
       <c r="W7" s="8" t="n">
         <v>16.6</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v>82.09999999999999</v>
-      </c>
+        <v>17.9</v>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
       <c r="Z7" s="3" t="n">
-        <v>0.1</v>
+        <v>39</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1116,43 +1131,41 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>229.8</v>
-      </c>
-      <c r="D8" s="11" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>21.6</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="G8" s="11" t="n">
+      <c r="E8" s="12" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="G8" s="12" t="n">
         <v>7.7</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>12.9</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>1.8</v>
+        <v>19.8</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>27.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>16.8</v>
-      </c>
+        <v>13.1</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="n">
-        <v>98</v>
+        <v>5.2</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.8</v>
@@ -1163,24 +1176,28 @@
       <c r="R8" s="3" t="n">
         <v>17.5</v>
       </c>
-      <c r="S8" s="8" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="n">
-        <v>76</v>
+        <v>140.1</v>
       </c>
       <c r="U8" s="3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="V8" s="17" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="X8" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="V8" s="3" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="inlineStr"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -1197,74 +1214,72 @@
       <c r="C9" s="3" t="n">
         <v>2224.9</v>
       </c>
-      <c r="D9" s="11" t="n">
-        <v>118.7</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>67.59999999999999</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>93.09999999999999</v>
-      </c>
-      <c r="G9" s="14" t="n">
-        <v>88.2</v>
+      <c r="D9" s="12" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>65.09999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>60.7</v>
+        <v>2650.4</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="L9" s="13" t="inlineStr"/>
+      <c r="M9" s="19" t="n">
+        <v>0.2</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>86</v>
+        <v>1.8</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>959</v>
+        <v>1.8</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="Q9" s="3" t="n">
-        <v>1194</v>
-      </c>
-      <c r="R9" s="3" t="n">
+      <c r="Q9" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="R9" s="19" t="n">
+        <v>2159</v>
+      </c>
+      <c r="S9" s="3" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="S9" s="3" t="n">
-        <v>6.8</v>
-      </c>
       <c r="T9" s="3" t="n">
-        <v>2162.6</v>
+        <v>86.2</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>959</v>
-      </c>
-      <c r="W9" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>312.6</v>
+      </c>
+      <c r="V9" s="19" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="W9" s="19" t="n">
+        <v>116</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>89.7</v>
+        <v>253</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>419.8</v>
+        <v>94</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>2</v>
+        <v>80.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1280,76 +1295,76 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>449</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E10" s="11" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E10" s="12" t="n">
         <v>13.5</v>
       </c>
-      <c r="F10" s="11" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="G10" s="11" t="n">
+      <c r="F10" s="19" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G10" s="3" t="n">
         <v>10.2</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>11.1</v>
+        <v>7.9</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>3.3</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>11.1</v>
+        <v>261.4</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="M10" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="M10" s="19" t="n">
         <v>13.8</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>15.8</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>91.8</v>
+        <v>921.8</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q10" s="8" t="n">
-        <v>27</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>17.6</v>
+        <v>11.3</v>
+      </c>
+      <c r="Q10" s="19" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="R10" s="19" t="n">
+        <v>87.59999999999999</v>
       </c>
       <c r="S10" s="3" t="n">
         <v>17.2</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>62.9</v>
+        <v>19.5</v>
       </c>
       <c r="U10" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="19" t="n">
         <v>18.8</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="19" t="n">
         <v>16.8</v>
       </c>
       <c r="X10" s="3" t="n">
         <v>17.9</v>
       </c>
       <c r="Y10" s="3" t="n">
+        <v>410.8</v>
+      </c>
+      <c r="Z10" s="3" t="n">
         <v>83</v>
-      </c>
-      <c r="Z10" s="3" t="n">
-        <v>3.8</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1367,73 +1382,71 @@
       <c r="C11" s="3" t="n">
         <v>221.8</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="12" t="n">
         <v>22.5</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>13.7</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="12" t="n">
         <v>18.1</v>
       </c>
-      <c r="G11" s="11" t="n">
-        <v>8.800000000000001</v>
-      </c>
+      <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>1.4</v>
+        <v>11.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K11" s="8" t="n">
-        <v>10.8</v>
+        <v>3.1</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>4.4</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>1.2</v>
+        <v>12.9</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>11.8</v>
+        <v>14.8</v>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="P11" s="8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q11" s="3" t="n">
-        <v>19.5</v>
+        <v>881.8</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="Q11" s="12" t="n">
+        <v>19.8</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="S11" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>28.4</v>
+        <v>1108.4</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X11" s="3" t="n">
-        <v>17.9</v>
+        <v>80.40000000000001</v>
+      </c>
+      <c r="V11" s="15" t="inlineStr"/>
+      <c r="W11" s="8" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="X11" s="8" t="n">
+        <v>717.5</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="Z11" s="3" t="inlineStr"/>
+        <v>71949</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>3.8</v>
+      </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -1448,25 +1461,25 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>229</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="G12" s="11" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F12" s="17" t="n">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="G12" s="3" t="n">
         <v>9.1</v>
       </c>
-      <c r="H12" s="8" t="n">
-        <v>13</v>
+      <c r="H12" s="3" t="n">
+        <v>11.3</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>1</v>
@@ -1474,49 +1487,51 @@
       <c r="K12" s="3" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="L12" s="3" t="n">
-        <v>11.4</v>
+      <c r="L12" s="8" t="n">
+        <v>14.8</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>83.5</v>
+        <v>13.9</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>12</v>
+        <v>15.9</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>92.8</v>
+        <v>991.8</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="Q12" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="R12" s="3" t="n">
+      <c r="Q12" s="12" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="R12" s="17" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="V12" s="3" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="W12" s="3" t="n">
         <v>17.1</v>
       </c>
-      <c r="S12" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V12" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="W12" s="3" t="n">
-        <v>14.8</v>
-      </c>
       <c r="X12" s="3" t="n">
-        <v>17.5</v>
+        <v>11.2</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>240.8</v>
-      </c>
-      <c r="Z12" s="3" t="inlineStr"/>
+        <v>44</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>11.8</v>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -1531,22 +1546,22 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="E13" s="11" t="n">
+        <v>1322</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="E13" s="12" t="n">
         <v>13.8</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="12" t="n">
         <v>18.7</v>
       </c>
-      <c r="G13" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>15.1</v>
+      <c r="G13" s="12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>13.5</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>1.4</v>
@@ -1554,53 +1569,51 @@
       <c r="J13" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="8" t="n">
         <v>15.7</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="M13" s="3" t="n">
-        <v>14.4</v>
+      <c r="M13" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="N13" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="Q13" s="12" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="R13" s="17" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V13" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="O13" s="3" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="R13" s="3" t="n">
+      <c r="W13" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="S13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T13" s="3" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="W13" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>15.1</v>
-      </c>
+      <c r="X13" s="3" t="inlineStr"/>
       <c r="Y13" s="3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>2.8</v>
+        <v>12.8</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1618,14 +1631,14 @@
       <c r="C14" s="3" t="n">
         <v>324</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>17.8</v>
+      <c r="D14" s="12" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>17.6</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>8.4</v>
@@ -1633,17 +1646,17 @@
       <c r="H14" s="3" t="n">
         <v>12.5</v>
       </c>
-      <c r="I14" s="8" t="n">
-        <v>21.4</v>
+      <c r="I14" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="L14" s="3" t="n">
-        <v>14.4</v>
+      <c r="L14" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>13.7</v>
@@ -1652,18 +1665,18 @@
         <v>15.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>94</v>
+        <v>228.1</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q14" s="12" t="n">
         <v>21.3</v>
       </c>
       <c r="R14" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="S14" s="3" t="n">
+      <c r="S14" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="T14" s="3" t="n">
@@ -1672,20 +1685,20 @@
       <c r="U14" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="V14" s="3" t="n">
-        <v>18</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>17.4</v>
+      <c r="V14" s="17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>194.9</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>87.5</v>
+        <v>92</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1703,72 +1716,72 @@
       <c r="C15" s="3" t="n">
         <v>307.9</v>
       </c>
-      <c r="D15" s="12" t="inlineStr"/>
-      <c r="E15" s="11" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>78.3</v>
+      <c r="D15" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>11.2</v>
+        <v>19.7</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>12.6</v>
+        <v>19.6</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>1.2</v>
+        <v>19.2</v>
       </c>
       <c r="J15" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>148.1</v>
+        <v>14.6</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>13.8</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="O15" s="3" t="n">
-        <v>96.8</v>
-      </c>
+        <v>15.6</v>
+      </c>
+      <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q15" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q15" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="R15" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="S15" s="3" t="n">
+      <c r="R15" s="12" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="S15" s="12" t="n">
         <v>16.9</v>
       </c>
-      <c r="T15" s="3" t="n">
+      <c r="T15" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="U15" s="3" t="n">
+      <c r="U15" s="12" t="n">
         <v>6.2</v>
       </c>
-      <c r="V15" s="3" t="n">
+      <c r="V15" s="17" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="W15" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W15" s="3" t="n">
-        <v>15.7</v>
-      </c>
       <c r="X15" s="3" t="n">
-        <v>1.7</v>
+        <v>18</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>92</v>
+        <v>16.6</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>1.6</v>
+        <v>17.9</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1784,76 +1797,72 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1972.2</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>114.8</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>649.4</v>
-      </c>
+        <v>29775.9</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>1114.8</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="n">
         <v>5.9</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>191.2</v>
-      </c>
-      <c r="M16" s="3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K16" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L16" s="19" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="M16" s="19" t="n">
         <v>69.40000000000001</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="O16" s="3" t="n">
-        <v>64.5</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="O16" s="3" t="inlineStr"/>
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" s="3" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>83.8</v>
+      <c r="Q16" s="12" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="R16" s="19" t="n">
+        <v>83.90000000000001</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>88.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>164.8</v>
+        <v>42.4</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>180.6</v>
+        <v>14.8</v>
+      </c>
+      <c r="V16" s="19" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="W16" s="19" t="n">
+        <v>18.6</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>488.8</v>
+        <v>450.4</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>2.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1871,50 +1880,50 @@
       <c r="C17" s="3" t="n">
         <v>225</v>
       </c>
-      <c r="D17" s="16" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>91.09999999999999</v>
+      <c r="D17" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>241.9</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="H17" s="8" t="n">
         <v>12.9</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J17" s="8" t="n">
-        <v>21.4</v>
+      <c r="J17" s="3" t="n">
+        <v>4.1</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>13.9</v>
+        <v>0.1</v>
+      </c>
+      <c r="L17" s="19" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="M17" s="19" t="n">
+        <v>12.1</v>
       </c>
       <c r="N17" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>912.9</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="Q17" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="O17" s="3" t="n">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="P17" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="R17" s="3" t="n">
-        <v>16.9</v>
+      <c r="R17" s="19" t="n">
+        <v>16.7</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>17.6</v>
@@ -1923,22 +1932,22 @@
         <v>18.9</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="V17" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="V17" s="19" t="n">
         <v>16.9</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="19" t="n">
         <v>15.7</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>2</v>
+        <v>20.9</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1956,30 +1965,28 @@
       <c r="C18" s="3" t="n">
         <v>428.8</v>
       </c>
-      <c r="D18" s="14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="F18" s="3" t="n">
+      <c r="D18" s="12" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="F18" s="12" t="n">
         <v>18.1</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>12.4</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>10.1</v>
+        <v>6.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="K18" s="15" t="inlineStr"/>
       <c r="L18" s="3" t="n">
         <v>14</v>
       </c>
@@ -1987,43 +1994,43 @@
         <v>15</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="S18" s="3" t="n">
+      <c r="S18" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>8</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>16.9</v>
+        <v>18.6</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X18" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>11</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>81.8</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2039,19 +2046,19 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>840.6</v>
-      </c>
-      <c r="D19" s="14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="F19" s="3" t="n">
+        <v>9440.6</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="F19" s="12" t="n">
         <v>19.5</v>
       </c>
-      <c r="G19" s="3" t="n">
-        <v>14</v>
+      <c r="G19" s="8" t="n">
+        <v>11.1</v>
       </c>
       <c r="H19" s="8" t="n">
         <v>12.1</v>
@@ -2063,31 +2070,31 @@
         <v>3.4</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>15.1</v>
+        <v>1.8</v>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>85.09999999999999</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>1.4</v>
+        <v>14.5</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>11.5</v>
+        <v>1.5</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>11.4</v>
+        <v>1.5</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="R19" s="3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R19" s="12" t="n">
         <v>18.1</v>
       </c>
-      <c r="S19" s="3" t="n">
-        <v>17</v>
+      <c r="S19" s="8" t="n">
+        <v>71.09999999999999</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>54</v>
@@ -2095,18 +2102,20 @@
       <c r="U19" s="8" t="n">
         <v>14.4</v>
       </c>
-      <c r="V19" s="3" t="inlineStr"/>
+      <c r="V19" s="3" t="n">
+        <v>19.8</v>
+      </c>
       <c r="W19" s="3" t="n">
-        <v>16.8</v>
+        <v>8.4</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>81</v>
+        <v>810.8</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>27.4</v>
+        <v>284.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2124,73 +2133,71 @@
       <c r="C20" s="3" t="n">
         <v>153.1</v>
       </c>
-      <c r="D20" s="11" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="F20" s="11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="G20" s="11" t="n">
-        <v>14</v>
+      <c r="D20" s="12" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>65.90000000000001</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>3.4</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="n">
         <v>5.6</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>19.4</v>
+        <v>13.4</v>
       </c>
       <c r="M20" s="3" t="n">
         <v>15.1</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.7</v>
+        <v>0.1</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>97</v>
+        <v>971</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="R20" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q20" s="17" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="R20" s="12" t="n">
         <v>17.6</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>76.8</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="V20" s="3" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="V20" s="12" t="n">
         <v>17.6</v>
       </c>
-      <c r="W20" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X20" s="3" t="n">
+      <c r="W20" s="12" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="X20" s="12" t="n">
         <v>18.6</v>
       </c>
-      <c r="Y20" s="3" t="n">
+      <c r="Y20" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="Z20" s="3" t="n">
+      <c r="Z20" s="12" t="n">
         <v>1.6</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -2209,71 +2216,71 @@
       <c r="C21" s="3" t="n">
         <v>261.7</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="E21" s="3" t="n">
+      <c r="D21" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E21" s="12" t="n">
         <v>14.7</v>
       </c>
-      <c r="F21" s="14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>11.9</v>
+      <c r="F21" s="12" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>11.1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>11.9</v>
+        <v>46.4</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="L21" s="3" t="n">
-        <v>16.4</v>
+      <c r="L21" s="8" t="n">
+        <v>22.1</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>15.2</v>
+        <v>15.9</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>1</v>
+        <v>11.7</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>90.8</v>
+        <v>919.8</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q21" s="8" t="n">
+      <c r="Q21" s="12" t="n">
         <v>21.5</v>
       </c>
-      <c r="R21" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="S21" s="3" t="n">
+      <c r="R21" s="12" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="S21" s="12" t="n">
         <v>18.9</v>
       </c>
-      <c r="T21" s="3" t="n">
+      <c r="T21" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="U21" s="3" t="n">
-        <v>6.8</v>
+      <c r="U21" s="12" t="n">
+        <v>6.6</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>17.6</v>
+        <v>18.5</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>11.9</v>
+        <v>11</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>880.9</v>
+        <v>188.4</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>2.8</v>
@@ -2294,61 +2301,63 @@
       <c r="C22" s="3" t="n">
         <v>123.3</v>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E22" s="14" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="F22" s="3" t="n">
+      <c r="D22" s="12" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F22" s="12" t="n">
         <v>17.5</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>13.4</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>1.8</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>11.9</v>
+        <v>0.2</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>911</v>
+        <v>91</v>
       </c>
       <c r="P22" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q22" s="3" t="n">
+      <c r="Q22" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="R22" s="3" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="S22" s="8" t="n">
+      <c r="R22" s="12" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="S22" s="12" t="n">
         <v>17.8</v>
       </c>
-      <c r="T22" s="3" t="n">
+      <c r="T22" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="U22" s="3" t="n">
+      <c r="U22" s="12" t="n">
         <v>6.2</v>
       </c>
-      <c r="V22" s="3" t="inlineStr"/>
+      <c r="V22" s="17" t="n">
+        <v>87</v>
+      </c>
       <c r="W22" s="3" t="n">
         <v>16.9</v>
       </c>
@@ -2356,10 +2365,10 @@
         <v>18.9</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>94.5</v>
+        <v>940.9</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2375,53 +2384,55 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1971.2</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>11153.1</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>940.8</v>
-      </c>
-      <c r="G23" s="3" t="n">
-        <v>43.1</v>
+        <v>1477.4</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>113</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>43.7</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>69.8</v>
+        <v>61.7</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>80.8</v>
+        <v>8</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>122.1</v>
-      </c>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>9.9</v>
+      </c>
+      <c r="K23" s="19" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="L23" s="19" t="n">
+        <v>162.2</v>
+      </c>
+      <c r="M23" s="19" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>98.8</v>
+      </c>
       <c r="O23" s="3" t="n">
-        <v>14.8</v>
+        <v>1461.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q23" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q23" s="19" t="n">
         <v>109</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="19" t="n">
         <v>88.8</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>90</v>
+        <v>90.5</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>347.9</v>
@@ -2429,17 +2440,17 @@
       <c r="U23" s="3" t="n">
         <v>40.6</v>
       </c>
-      <c r="V23" s="3" t="n">
-        <v>918.9</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>89.90000000000001</v>
+      <c r="V23" s="19" t="n">
+        <v>918.8</v>
+      </c>
+      <c r="W23" s="19" t="n">
+        <v>611.5</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>911.8</v>
+        <v>98.2</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>48.4</v>
+        <v>4555.4</v>
       </c>
       <c r="Z23" s="3" t="n">
         <v>113.8</v>
@@ -2458,22 +2469,22 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>215.4</v>
-      </c>
-      <c r="D24" s="16" t="n">
+        <v>295.4</v>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>22.7</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="E24" s="12" t="n">
         <v>13.9</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="F24" s="12" t="n">
         <v>18.2</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="12" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>69.8</v>
+        <v>18.9</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>1.5</v>
@@ -2482,51 +2493,51 @@
         <v>1.9</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>38.2</v>
-      </c>
-      <c r="L24" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L24" s="19" t="n">
         <v>15.2</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="19" t="n">
         <v>14.4</v>
       </c>
       <c r="N24" s="3" t="n">
         <v>1.6</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>92.40000000000001</v>
+        <v>21.1</v>
       </c>
       <c r="P24" s="3" t="n">
         <v>1.4</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="19" t="n">
         <v>21.8</v>
       </c>
-      <c r="R24" s="3" t="n">
-        <v>47.8</v>
+      <c r="R24" s="19" t="n">
+        <v>17.8</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>18.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>69.5</v>
+        <v>14696.4</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V24" s="3" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="W24" s="3" t="n">
+      <c r="V24" s="19" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="W24" s="19" t="n">
         <v>16.8</v>
       </c>
-      <c r="X24" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="Y24" s="3" t="n">
+      <c r="X24" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="Y24" s="12" t="n">
         <v>87.09999999999999</v>
       </c>
-      <c r="Z24" s="3" t="n">
+      <c r="Z24" s="12" t="n">
         <v>2.8</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -2543,58 +2554,54 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>490.4</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>15</v>
+        <v>2100.4</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>15.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H25" s="8" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J25" s="8" t="n">
-        <v>18.1</v>
+        <v>4.6</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr"/>
+      <c r="J25" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="M25" s="8" t="n">
-        <v>849.2</v>
+        <v>15.1</v>
+      </c>
+      <c r="M25" s="17" t="n">
+        <v>84.2</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>15.4</v>
+        <v>1.5</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>910.8</v>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q25" s="8" t="n">
-        <v>1.9</v>
+        <v>44.6</v>
+      </c>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="R25" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S25" s="3" t="n">
-        <v>11.6</v>
+        <v>11.9</v>
+      </c>
+      <c r="S25" s="8" t="n">
+        <v>15.6</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="U25" s="3" t="n">
         <v>8</v>
@@ -2602,17 +2609,17 @@
       <c r="V25" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="W25" s="8" t="n">
-        <v>12.9</v>
+      <c r="W25" s="17" t="n">
+        <v>1.2</v>
       </c>
       <c r="X25" s="3" t="n">
-        <v>18.1</v>
+        <v>43.1</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>94</v>
+        <v>94.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>2.8</v>
+        <v>1.2</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2628,76 +2635,72 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>281.8</v>
-      </c>
-      <c r="D26" s="11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E26" s="11" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G26" s="11" t="n">
+        <v>226</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="G26" s="12" t="n">
         <v>8.9</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>1.4</v>
-      </c>
+        <v>12.9</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="L26" s="8" t="n">
-        <v>84.59999999999999</v>
-      </c>
-      <c r="M26" s="3" t="n">
-        <v>14.9</v>
+        <v>3.9</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr"/>
+      <c r="M26" s="8" t="n">
+        <v>14.1</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>95</v>
+        <v>900.8</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="R26" s="3" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="S26" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q26" s="17" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="R26" s="8" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="S26" s="8" t="n">
         <v>17.8</v>
       </c>
       <c r="T26" s="3" t="n">
-        <v>73</v>
+        <v>713</v>
       </c>
       <c r="U26" s="3" t="n">
         <v>6.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="W26" s="3" t="n">
-        <v>16.2</v>
+        <v>15.9</v>
+      </c>
+      <c r="W26" s="8" t="n">
+        <v>26.8</v>
       </c>
       <c r="X26" s="8" t="n">
         <v>18</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>88.5</v>
+        <v>28.2</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2713,76 +2716,76 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>305.9</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="G27" s="3" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D27" s="12" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="G27" s="12" t="n">
         <v>9.1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>24.2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>21.9</v>
+        <v>24.1</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="L27" s="8" t="n">
+      <c r="L27" s="3" t="n">
         <v>15.4</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.8</v>
+        <v>16.9</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>94</v>
+        <v>94.8</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q27" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="R27" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S27" s="8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q27" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="R27" s="8" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="S27" s="3" t="n">
         <v>19</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>11</v>
+        <v>717</v>
       </c>
       <c r="U27" s="3" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="V27" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>16.8</v>
+        <v>15.8</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>18.5</v>
+        <v>18.8</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>91</v>
+        <v>91.8</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2798,76 +2801,74 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>2023.9</v>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="F28" s="11" t="n">
+        <v>2305.9</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="F28" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="G28" s="11" t="n">
-        <v>8</v>
+      <c r="G28" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>22.8</v>
+        <v>80.8</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>21.9</v>
+        <v>1.5</v>
       </c>
       <c r="K28" s="8" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="L28" s="3" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="L28" s="8" t="n">
         <v>14.7</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>14.2</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>95</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>20.5</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q28" s="17" t="n">
+        <v>0.8</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>17</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>17.2</v>
+        <v>17.9</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>72.8</v>
       </c>
-      <c r="U28" s="3" t="n">
-        <v>66.09999999999999</v>
-      </c>
+      <c r="U28" s="3" t="inlineStr"/>
       <c r="V28" s="3" t="n">
         <v>16.7</v>
       </c>
-      <c r="W28" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="X28" s="3" t="n">
+      <c r="W28" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="X28" s="8" t="n">
         <v>15.8</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>83.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>3.2</v>
+        <v>289.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2883,76 +2884,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>289.8</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>21.4</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v>23.8</v>
+        <v>181</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>39.8</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="M29" s="3" t="n">
-        <v>14.4</v>
+        <v>86.7</v>
+      </c>
+      <c r="L29" s="8" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="M29" s="17" t="n">
+        <v>84.40000000000001</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>16.5</v>
+        <v>1.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>95</v>
+        <v>99.8</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="Q29" s="8" t="n">
-        <v>21.3</v>
+        <v>0.8</v>
+      </c>
+      <c r="Q29" s="17" t="n">
+        <v>1.2</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="S29" s="3" t="n">
-        <v>18.2</v>
+        <v>8</v>
+      </c>
+      <c r="S29" s="8" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>70</v>
+        <v>710</v>
       </c>
       <c r="U29" s="3" t="n">
-        <v>7.8</v>
+        <v>27.8</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="W29" s="3" t="n">
-        <v>17.1</v>
+      <c r="W29" s="17" t="n">
+        <v>87.09999999999999</v>
       </c>
       <c r="X29" s="3" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>3.2</v>
+        <v>13.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2968,76 +2969,72 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>1682.9</v>
-      </c>
-      <c r="D30" s="11" t="n">
-        <v>104.9</v>
-      </c>
-      <c r="E30" s="11" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="F30" s="11" t="n">
-        <v>87.3</v>
+        <v>1699.9</v>
+      </c>
+      <c r="D30" s="19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E30" s="13" t="inlineStr"/>
+      <c r="F30" s="19" t="n">
+        <v>90.59999999999999</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>43.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>80.59999999999999</v>
+        <v>860.6</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>65.59999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>456.6</v>
-      </c>
-      <c r="L30" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="M30" s="3" t="n">
-        <v>11.1</v>
+      <c r="K30" s="19" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="L30" s="13" t="inlineStr"/>
+      <c r="M30" s="19" t="n">
+        <v>17.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>71.8</v>
+        <v>79.8</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>20021.4</v>
+        <v>479.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="R30" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>5</v>
+      </c>
+      <c r="Q30" s="19" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="R30" s="19" t="n">
+        <v>83.40000000000001</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>4</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>561.9</v>
+        <v>961.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>394.6</v>
-      </c>
-      <c r="V30" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="W30" s="3" t="n">
+        <v>246.1</v>
+      </c>
+      <c r="V30" s="19" t="n">
+        <v>1828.8</v>
+      </c>
+      <c r="W30" s="19" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="X30" s="3" t="n">
-        <v>18.8</v>
+        <v>8820.9</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>441.8</v>
+        <v>444</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>112.2</v>
+        <v>25.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3055,35 +3052,33 @@
       <c r="C31" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="D31" s="19" t="n">
         <v>22.5</v>
       </c>
-      <c r="E31" s="11" t="n">
+      <c r="E31" s="12" t="n">
         <v>13.7</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="F31" s="19" t="n">
         <v>18.1</v>
       </c>
-      <c r="G31" s="11" t="n">
+      <c r="G31" s="12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>22.8</v>
+        <v>18.3</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1.3</v>
+        <v>11.3</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>456.6</v>
-      </c>
+      <c r="K31" s="3" t="inlineStr"/>
       <c r="L31" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="M31" s="19" t="n">
         <v>14.9</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>14.3</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>16.8</v>
@@ -3094,35 +3089,35 @@
       <c r="P31" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="19" t="n">
         <v>21</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="19" t="n">
         <v>17.5</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>18.1</v>
+        <v>10.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>561.9</v>
+        <v>29.7</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>6.9</v>
       </c>
-      <c r="V31" s="8" t="n">
+      <c r="V31" s="19" t="n">
         <v>17.6</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="19" t="n">
         <v>16.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>17.7</v>
+        <v>1.1</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>88.8</v>
+        <v>15.2</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>941.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3138,76 +3133,76 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>482.8</v>
-      </c>
-      <c r="D32" s="11" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>19.3</v>
+        <v>6.2</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>11.9</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>19.4</v>
+        <v>45.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>12.3</v>
+        <v>12.7</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>14.9</v>
+        <v>16.3</v>
+      </c>
+      <c r="M32" s="17" t="n">
+        <v>46.1</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>16.8</v>
+        <v>19.2</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>895</v>
+        <v>610.4</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="R32" s="8" t="n">
-        <v>19.8</v>
+      <c r="R32" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="S32" s="3" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>444.8</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="V32" s="17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="W32" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="T32" s="3" t="n">
-        <v>901.1</v>
-      </c>
-      <c r="U32" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V32" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="W32" s="8" t="n">
-        <v>16.6</v>
-      </c>
       <c r="X32" s="3" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>91</v>
+        <v>15.6</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>8</v>
+        <v>11.9</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3226,67 +3221,65 @@
         <v>482.8</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <v>39.7</v>
+        <v>14.8</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>18.5</v>
       </c>
       <c r="G33" s="8" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>8.199999999999999</v>
+        <v>19.7</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>88.59999999999999</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.6</v>
+        <v>12.6</v>
       </c>
       <c r="J33" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="L33" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L33" s="17" t="n">
         <v>1.2</v>
       </c>
-      <c r="M33" s="3" t="n">
-        <v>13</v>
+      <c r="M33" s="17" t="n">
+        <v>1.7</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>15.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>93</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q33" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q33" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>16.8</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>12</v>
+      <c r="S33" s="8" t="n">
+        <v>92.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v>14.4</v>
-      </c>
+        <v>21.8</v>
+      </c>
+      <c r="U33" s="3" t="inlineStr"/>
       <c r="V33" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="W33" s="8" t="n">
-        <v>83.40000000000001</v>
+      <c r="W33" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="X33" s="3" t="n">
-        <v>16</v>
+        <v>10.8</v>
       </c>
       <c r="Y33" s="3" t="n">
         <v>71.8</v>
@@ -3308,54 +3301,54 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>492.8</v>
-      </c>
-      <c r="D34" s="11" t="n">
+        <v>482.8</v>
+      </c>
+      <c r="D34" s="12" t="n">
         <v>24.1</v>
       </c>
-      <c r="E34" s="11" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="F34" s="11" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="G34" s="3" t="n">
+      <c r="E34" s="12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="G34" s="12" t="n">
         <v>12.6</v>
       </c>
-      <c r="H34" s="8" t="n">
-        <v>8.300000000000001</v>
+      <c r="H34" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>23.1</v>
+        <v>2.5</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>3.9</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="M34" s="8" t="n">
-        <v>11.6</v>
+        <v>0</v>
+      </c>
+      <c r="L34" s="17" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>1.1</v>
+        <v>19.8</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>92</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>23.9</v>
+        <v>1.2</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>28.9</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="S34" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="S34" s="8" t="n">
         <v>16.8</v>
       </c>
       <c r="T34" s="3" t="n">
@@ -3365,17 +3358,19 @@
         <v>12.8</v>
       </c>
       <c r="V34" s="3" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="W34" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X34" s="3" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>12</v>
+      </c>
       <c r="Y34" s="3" t="n">
-        <v>21</v>
+        <v>119.6</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>89.2</v>
+        <v>113.1</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3391,23 +3386,21 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>172.6</v>
+        <v>9422.799999999999</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="E35" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>13.6</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="G35" s="8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="H35" s="8" t="n">
-        <v>8.300000000000001</v>
-      </c>
+      <c r="F35" s="8" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H35" s="3" t="inlineStr"/>
       <c r="I35" s="3" t="n">
         <v>2.4</v>
       </c>
@@ -3415,50 +3408,52 @@
         <v>4</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>10</v>
+        <v>0.9</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>16.6</v>
       </c>
-      <c r="M35" s="8" t="n">
-        <v>13.5</v>
+      <c r="M35" s="3" t="n">
+        <v>15.5</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>1.7</v>
+        <v>18.8</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>9180</v>
+        <v>190</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q35" s="3" t="n">
-        <v>29.8</v>
+        <v>2</v>
+      </c>
+      <c r="Q35" s="8" t="n">
+        <v>14.9</v>
       </c>
       <c r="R35" s="3" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="S35" s="3" t="n">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>600.8</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>12.8</v>
+        <v>68</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>12.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>20.7</v>
+        <v>20.1</v>
       </c>
       <c r="W35" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="X35" s="3" t="inlineStr"/>
+        <v>11.8</v>
+      </c>
+      <c r="X35" s="8" t="n">
+        <v>80</v>
+      </c>
       <c r="Y35" s="3" t="n">
-        <v>75.5</v>
+        <v>79.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>6</v>
+        <v>9498.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3474,23 +3469,25 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>498.3</v>
-      </c>
-      <c r="D36" s="11" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="E36" s="11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="F36" s="11" t="n">
+        <v>164.1</v>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>192.1</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F36" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="G36" s="11" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>12.7</v>
+      </c>
       <c r="I36" s="3" t="n">
-        <v>2.3</v>
+        <v>22.8</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>4</v>
@@ -3498,47 +3495,47 @@
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L36" s="3" t="n">
-        <v>16.6</v>
+      <c r="L36" s="17" t="n">
+        <v>86.59999999999999</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>18.9</v>
+      <c r="N36" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>91</v>
+        <v>911.8</v>
       </c>
       <c r="P36" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q36" s="8" t="n">
-        <v>129.2</v>
+      <c r="Q36" s="17" t="n">
+        <v>14.11</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S36" s="8" t="n">
-        <v>71</v>
+        <v>17.2</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>552.1</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>12.8</v>
+        <v>22.9</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>1.2</v>
       </c>
       <c r="V36" s="3" t="n">
-        <v>18.4</v>
+        <v>10.9</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>1.6</v>
+        <v>16.6</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>79.8</v>
+        <v>719.8</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>4.5</v>
@@ -3557,76 +3554,74 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2122</v>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>119.1</v>
-      </c>
-      <c r="E37" s="11" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>22.6</v>
+        <v>2192.8</v>
+      </c>
+      <c r="D37" s="13" t="inlineStr"/>
+      <c r="E37" s="19" t="n">
+        <v>165.8</v>
+      </c>
+      <c r="F37" s="19" t="n">
+        <v>92.59999999999999</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>22.9</v>
+        <v>53.2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>4</v>
+        <v>18.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>110.8</v>
+        <v>110.6</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v>122.9</v>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>8012</v>
+        <v>117.6</v>
+      </c>
+      <c r="K37" s="19" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="L37" s="19" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="M37" s="19" t="n">
+        <v>211.2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>19.1</v>
+        <v>118.6</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>449</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Q37" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q37" s="19" t="n">
         <v>113.4</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="19" t="n">
         <v>1</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>84.8</v>
+        <v>34.8</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>313.4</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="W37" s="3" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="V37" s="19" t="n">
+        <v>91</v>
+      </c>
+      <c r="W37" s="19" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>82</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>940.2</v>
+        <v>408.8</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>128.1</v>
+        <v>28.1</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3642,76 +3637,76 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>9438.6</v>
-      </c>
-      <c r="D38" s="16" t="n">
+        <v>43.8</v>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>23.8</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="19" t="n">
         <v>13.2</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="F38" s="19" t="n">
         <v>18.5</v>
       </c>
-      <c r="G38" s="11" t="n">
-        <v>10.5</v>
+      <c r="G38" s="12" t="n">
+        <v>10.8</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>12.3</v>
+        <v>18.9</v>
       </c>
       <c r="I38" s="3" t="n">
         <v>12.1</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="K38" s="8" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="L38" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L38" s="19" t="n">
         <v>15.1</v>
       </c>
-      <c r="M38" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>52.1</v>
+      <c r="M38" s="19" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="N38" s="3" t="n">
+        <v>15.8</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>89.8</v>
+        <v>676.4</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="Q38" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q38" s="19" t="n">
         <v>22.7</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="19" t="n">
         <v>17.4</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>17</v>
+        <v>17.8</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>313.4</v>
-      </c>
-      <c r="U38" s="3" t="n">
+        <v>682.8</v>
+      </c>
+      <c r="U38" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="19" t="n">
         <v>18.2</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="19" t="n">
         <v>16.1</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>17.1</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>940.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3727,76 +3722,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>395</v>
-      </c>
-      <c r="D39" s="14" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="E39" s="14" t="n">
-        <v>92</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>18.7</v>
+        <v>395.3</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>37.8</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H39" s="3" t="n">
-        <v>12.3</v>
+        <v>11.9</v>
+      </c>
+      <c r="H39" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>23.2</v>
+        <v>13.2</v>
+      </c>
+      <c r="J39" s="8" t="n">
+        <v>52.4</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="L39" s="3" t="n">
-        <v>18.8</v>
+        <v>0</v>
+      </c>
+      <c r="L39" s="17" t="n">
+        <v>46.1</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>150.1</v>
+        <v>11.5</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>18.9</v>
+        <v>3.6</v>
       </c>
       <c r="O39" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q39" s="8" t="n">
-        <v>19.6</v>
+        <v>18.8</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>16.6</v>
+        <v>15.6</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>71</v>
+        <v>52</v>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v>949</v>
+      </c>
+      <c r="V39" s="17" t="n">
+        <v>19.1</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>1.9</v>
+        <v>12.1</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>15.8</v>
+        <v>45.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>11.8</v>
+        <v>74</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3812,16 +3807,16 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>2942.1</v>
-      </c>
-      <c r="D40" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="E40" s="14" t="n">
-        <v>92</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>49.4</v>
+        <v>9945.1</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>19.8</v>
       </c>
       <c r="G40" s="8" t="n">
         <v>10.7</v>
@@ -3830,56 +3825,58 @@
         <v>11.5</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>4.7</v>
+      </c>
       <c r="K40" s="3" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="L40" s="8" t="n">
-        <v>16</v>
+        <v>11</v>
+      </c>
+      <c r="L40" s="17" t="n">
+        <v>96</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="N40" s="8" t="n">
-        <v>38.9</v>
+        <v>19</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>10.9</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="R40" s="3" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="S40" s="3" t="n">
-        <v>17.2</v>
+        <v>13.8</v>
+      </c>
+      <c r="R40" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="S40" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>68.5</v>
+        <v>68.8</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V40" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="W40" s="3" t="n">
+      <c r="V40" s="17" t="n">
+        <v>89.90000000000001</v>
+      </c>
+      <c r="W40" s="8" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="X40" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="X40" s="3" t="n">
-        <v>16.8</v>
-      </c>
       <c r="Y40" s="3" t="n">
-        <v>72</v>
+        <v>12.6</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3897,69 +3894,71 @@
       <c r="C41" s="3" t="n">
         <v>408.4</v>
       </c>
-      <c r="D41" s="11" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F41" s="11" t="n">
+      <c r="D41" s="3" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="G41" s="11" t="n">
-        <v>11.1</v>
+      <c r="G41" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>10.8</v>
       </c>
-      <c r="I41" s="8" t="n">
-        <v>11.1</v>
+      <c r="I41" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="M41" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M41" s="8" t="n">
         <v>13.6</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>19.2</v>
+        <v>1.1</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>2</v>
+        <v>22.9</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>17.9</v>
+        <v>18.8</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>17.8</v>
+        <v>15</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>68.5</v>
+        <v>162.2</v>
       </c>
       <c r="U41" s="3" t="n">
-        <v>12</v>
+        <v>18.2</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="W41" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="X41" s="3" t="inlineStr"/>
+        <v>19.8</v>
+      </c>
+      <c r="W41" s="17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>1.1</v>
+      </c>
       <c r="Y41" s="3" t="n">
-        <v>83</v>
+        <v>2.6</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>3.8</v>
@@ -3978,64 +3977,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>349.1</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr"/>
-      <c r="E42" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="F42" s="14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="8" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="I42" s="3" t="inlineStr"/>
+        <v>340.1</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="G42" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>11.7</v>
+      </c>
       <c r="J42" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="3" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
+      </c>
+      <c r="L42" s="17" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="M42" s="17" t="n">
+        <v>11.38</v>
       </c>
       <c r="N42" s="3" t="n">
-        <v>14.6</v>
+        <v>12.9</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>88.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="P42" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="Q42" s="3" t="n">
+        <v>22</v>
+      </c>
       <c r="R42" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="S42" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="S42" s="8" t="n">
+        <v>608</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>60.8</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="W42" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="T42" s="3" t="n">
-        <v>289.5</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="X42" s="3" t="inlineStr"/>
+      <c r="X42" s="8" t="n">
+        <v>10.2</v>
+      </c>
       <c r="Y42" s="3" t="n">
-        <v>87</v>
+        <v>1.4</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>2.6</v>
+        <v>20.6</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4051,63 +4062,73 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>517</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
+        <v>257.1</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>10.1</v>
+      </c>
       <c r="F43" s="3" t="n">
         <v>18.1</v>
       </c>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="8" t="n">
+      <c r="G43" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="M43" s="8" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="P43" s="3" t="n">
         <v>11.4</v>
-      </c>
-      <c r="I43" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="M43" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N43" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="O43" s="3" t="n">
-        <v>82</v>
-      </c>
-      <c r="P43" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>22.2</v>
       </c>
       <c r="R43" s="3" t="n">
-        <v>1.6</v>
+        <v>16.5</v>
       </c>
       <c r="S43" s="3" t="n">
-        <v>15.6</v>
+        <v>12.6</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="W43" s="3" t="inlineStr"/>
-      <c r="X43" s="3" t="n">
-        <v>16.2</v>
+        <v>58.8</v>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="X43" s="8" t="n">
+        <v>501.4</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>81.8</v>
+        <v>201</v>
       </c>
       <c r="Z43" s="3" t="n">
         <v>3.7</v>
@@ -4126,23 +4147,25 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>653.1</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="F44" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>2.6</v>
+        <v>257.1</v>
+      </c>
+      <c r="D44" s="8" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="J44" s="3" t="n">
         <v>5</v>
@@ -4151,38 +4174,50 @@
         <v>0</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="N44" s="3" t="inlineStr"/>
+        <v>13.9</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>11.1</v>
+      </c>
       <c r="O44" s="3" t="n">
         <v>91</v>
       </c>
       <c r="P44" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="Q44" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="R44" s="8" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>13.9</v>
+        <v>1.9</v>
+      </c>
+      <c r="Q44" s="8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="R44" s="17" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="S44" s="8" t="n">
+        <v>28.3</v>
       </c>
       <c r="T44" s="3" t="n">
-        <v>59.5</v>
-      </c>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="W44" s="3" t="inlineStr"/>
-      <c r="X44" s="3" t="inlineStr"/>
-      <c r="Y44" s="3" t="inlineStr"/>
-      <c r="Z44" s="3" t="inlineStr"/>
+        <v>99.3</v>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="W44" s="17" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v>183.6</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>17.8</v>
+      </c>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4197,70 +4232,76 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2283</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>198.5</v>
-      </c>
-      <c r="E45" s="13" t="inlineStr"/>
-      <c r="F45" s="16" t="n">
-        <v>110.8</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>2</v>
+        <v>2983</v>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>191.7</v>
+      </c>
+      <c r="E45" s="19" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>16.2</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>128.8</v>
+        <v>10.8</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>13.2</v>
+        <v>15.2</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="K45" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>88</v>
+      <c r="K45" s="19" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="L45" s="19" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="M45" s="19" t="n">
+        <v>82</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>91.8</v>
+        <v>81.8</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>290.9</v>
+        <v>28981.1</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>112.6</v>
-      </c>
-      <c r="Q45" s="3" t="n">
-        <v>137</v>
-      </c>
-      <c r="R45" s="3" t="inlineStr"/>
+        <v>110.6</v>
+      </c>
+      <c r="Q45" s="19" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="R45" s="19" t="n">
+        <v>10.2</v>
+      </c>
       <c r="S45" s="3" t="n">
-        <v>99.8</v>
+        <v>97.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>381</v>
-      </c>
-      <c r="U45" s="3" t="inlineStr"/>
-      <c r="V45" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>89</v>
+      </c>
+      <c r="V45" s="19" t="n">
         <v>111.8</v>
       </c>
-      <c r="W45" s="3" t="n">
-        <v>220.8</v>
+      <c r="W45" s="19" t="n">
+        <v>77.7</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>89.59999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>4648.4</v>
+        <v>4658.8</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>28.1</v>
+        <v>28.7</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4276,22 +4317,20 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>498</v>
-      </c>
-      <c r="D46" s="16" t="n">
+        <v>2497</v>
+      </c>
+      <c r="D46" s="19" t="n">
         <v>23.5</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="19" t="n">
         <v>13.2</v>
       </c>
-      <c r="F46" s="16" t="n">
+      <c r="F46" s="19" t="n">
         <v>18.5</v>
       </c>
-      <c r="G46" s="11" t="n">
-        <v>10.3</v>
-      </c>
+      <c r="G46" s="3" t="inlineStr"/>
       <c r="H46" s="3" t="n">
-        <v>11.8</v>
+        <v>44.8</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.5</v>
@@ -4300,44 +4339,50 @@
         <v>4.4</v>
       </c>
       <c r="K46" s="3" t="inlineStr"/>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="19" t="n">
         <v>14.9</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="N46" s="3" t="inlineStr"/>
+      <c r="M46" s="19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>15.2</v>
+      </c>
       <c r="O46" s="3" t="n">
-        <v>201.1</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="R46" s="3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q46" s="19" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="R46" s="19" t="n">
         <v>17.1</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="W46" s="8" t="n">
+        <v>858.5</v>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="V46" s="19" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="W46" s="19" t="n">
         <v>15.9</v>
       </c>
-      <c r="X46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="n">
+        <v>16.6</v>
+      </c>
       <c r="Y46" s="3" t="n">
-        <v>87.8</v>
+        <v>118.4</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>4.8</v>
+        <v>11.4</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
